--- a/EduMultiPro 2 Parte/2-Normalizacion 3FN/Normalizacion.xlsx
+++ b/EduMultiPro 2 Parte/2-Normalizacion 3FN/Normalizacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\EduMultiPro\EduMultiPro 2 Parte\2-Normalizacion 3FN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67ECFFEF-ECBC-4A09-9919-375C19ED8707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38BC18B-0E5B-4464-966F-CD91E367EB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tablas" sheetId="6" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="234">
   <si>
     <t>Rol</t>
   </si>
@@ -680,6 +680,51 @@
   </si>
   <si>
     <t>ID Usuarios</t>
+  </si>
+  <si>
+    <t>Trabajos Entregado Archivo</t>
+  </si>
+  <si>
+    <t>TEA001</t>
+  </si>
+  <si>
+    <t>TEA002</t>
+  </si>
+  <si>
+    <t>TEA003</t>
+  </si>
+  <si>
+    <t>RutaArchivo</t>
+  </si>
+  <si>
+    <t>NombreOriginal</t>
+  </si>
+  <si>
+    <t>Archivo1</t>
+  </si>
+  <si>
+    <t>Archivo2</t>
+  </si>
+  <si>
+    <t>Archivo3</t>
+  </si>
+  <si>
+    <t>Trabajos Archivo</t>
+  </si>
+  <si>
+    <t>ID Archivo entregados</t>
+  </si>
+  <si>
+    <t>ID Trabajo Archivo</t>
+  </si>
+  <si>
+    <t>TA001</t>
+  </si>
+  <si>
+    <t>TA002</t>
+  </si>
+  <si>
+    <t>TA003</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1219,7 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="498">
+  <dxfs count="494">
     <dxf>
       <font>
         <b val="0"/>
@@ -1184,6 +1229,182 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFD9E7FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
@@ -1199,6 +1420,436 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFD9E7FD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1221,13 +1872,75 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1246,6 +1959,506 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFD9E7FD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFD9E7FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1271,6 +2484,23 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1296,6 +2526,22 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1348,7 +2594,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1380,6 +2628,349 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
@@ -1395,14 +2986,14 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <border>
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -1424,11 +3015,88 @@
           <bgColor rgb="FFD9E7FD"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
         <bottom style="thin">
           <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -1441,38 +3109,7 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
@@ -1487,469 +3124,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFD9E7FD"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1969,1321 +3143,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFD9E7FD"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFD9E7FD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFD9E7FD"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3881,6 +3740,31 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3993,6 +3877,31 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -5814,6 +5723,22 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -5837,6 +5762,1120 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -5859,20 +6898,33 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5883,7 +6935,7 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
@@ -5897,10 +6949,17 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -5915,21 +6974,57 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -5948,14 +7043,13 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -5980,7 +7074,7 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
@@ -5988,7 +7082,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -6020,7 +7113,7 @@
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
@@ -6028,125 +7121,62 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -6155,6 +7185,27 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -6191,24 +7242,13 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -6219,14 +7259,10 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color theme="2"/>
@@ -6240,7 +7276,7 @@
           <bgColor theme="4"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -6253,22 +7289,118 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -6294,23 +7426,118 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -6333,1360 +7560,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="2"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -13728,79 +13601,79 @@
   </dxfs>
   <tableStyles count="15">
     <tableStyle name="Hoja 1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="497"/>
-      <tableStyleElement type="firstRowStripe" dxfId="496"/>
-      <tableStyleElement type="secondRowStripe" dxfId="495"/>
+      <tableStyleElement type="headerRow" dxfId="493"/>
+      <tableStyleElement type="firstRowStripe" dxfId="492"/>
+      <tableStyleElement type="secondRowStripe" dxfId="491"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 2" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="494"/>
-      <tableStyleElement type="firstRowStripe" dxfId="493"/>
-      <tableStyleElement type="secondRowStripe" dxfId="492"/>
+      <tableStyleElement type="headerRow" dxfId="490"/>
+      <tableStyleElement type="firstRowStripe" dxfId="489"/>
+      <tableStyleElement type="secondRowStripe" dxfId="488"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 3" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="491"/>
-      <tableStyleElement type="firstRowStripe" dxfId="490"/>
-      <tableStyleElement type="secondRowStripe" dxfId="489"/>
+      <tableStyleElement type="headerRow" dxfId="487"/>
+      <tableStyleElement type="firstRowStripe" dxfId="486"/>
+      <tableStyleElement type="secondRowStripe" dxfId="485"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 4" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="headerRow" dxfId="488"/>
-      <tableStyleElement type="firstRowStripe" dxfId="487"/>
-      <tableStyleElement type="secondRowStripe" dxfId="486"/>
+      <tableStyleElement type="headerRow" dxfId="484"/>
+      <tableStyleElement type="firstRowStripe" dxfId="483"/>
+      <tableStyleElement type="secondRowStripe" dxfId="482"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 5" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="headerRow" dxfId="485"/>
-      <tableStyleElement type="firstRowStripe" dxfId="484"/>
-      <tableStyleElement type="secondRowStripe" dxfId="483"/>
+      <tableStyleElement type="headerRow" dxfId="481"/>
+      <tableStyleElement type="firstRowStripe" dxfId="480"/>
+      <tableStyleElement type="secondRowStripe" dxfId="479"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 6" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="headerRow" dxfId="482"/>
-      <tableStyleElement type="firstRowStripe" dxfId="481"/>
-      <tableStyleElement type="secondRowStripe" dxfId="480"/>
+      <tableStyleElement type="headerRow" dxfId="478"/>
+      <tableStyleElement type="firstRowStripe" dxfId="477"/>
+      <tableStyleElement type="secondRowStripe" dxfId="476"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 7" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="headerRow" dxfId="479"/>
-      <tableStyleElement type="firstRowStripe" dxfId="478"/>
-      <tableStyleElement type="secondRowStripe" dxfId="477"/>
+      <tableStyleElement type="headerRow" dxfId="475"/>
+      <tableStyleElement type="firstRowStripe" dxfId="474"/>
+      <tableStyleElement type="secondRowStripe" dxfId="473"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 8" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="headerRow" dxfId="476"/>
-      <tableStyleElement type="firstRowStripe" dxfId="475"/>
-      <tableStyleElement type="secondRowStripe" dxfId="474"/>
+      <tableStyleElement type="headerRow" dxfId="472"/>
+      <tableStyleElement type="firstRowStripe" dxfId="471"/>
+      <tableStyleElement type="secondRowStripe" dxfId="470"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 9" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
-      <tableStyleElement type="headerRow" dxfId="473"/>
-      <tableStyleElement type="firstRowStripe" dxfId="472"/>
-      <tableStyleElement type="secondRowStripe" dxfId="471"/>
+      <tableStyleElement type="headerRow" dxfId="469"/>
+      <tableStyleElement type="firstRowStripe" dxfId="468"/>
+      <tableStyleElement type="secondRowStripe" dxfId="467"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 10" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
-      <tableStyleElement type="headerRow" dxfId="470"/>
-      <tableStyleElement type="firstRowStripe" dxfId="469"/>
-      <tableStyleElement type="secondRowStripe" dxfId="468"/>
+      <tableStyleElement type="headerRow" dxfId="466"/>
+      <tableStyleElement type="firstRowStripe" dxfId="465"/>
+      <tableStyleElement type="secondRowStripe" dxfId="464"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 11" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
-      <tableStyleElement type="headerRow" dxfId="467"/>
-      <tableStyleElement type="firstRowStripe" dxfId="466"/>
-      <tableStyleElement type="secondRowStripe" dxfId="465"/>
+      <tableStyleElement type="headerRow" dxfId="463"/>
+      <tableStyleElement type="firstRowStripe" dxfId="462"/>
+      <tableStyleElement type="secondRowStripe" dxfId="461"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 12" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
-      <tableStyleElement type="headerRow" dxfId="464"/>
-      <tableStyleElement type="firstRowStripe" dxfId="463"/>
-      <tableStyleElement type="secondRowStripe" dxfId="462"/>
+      <tableStyleElement type="headerRow" dxfId="460"/>
+      <tableStyleElement type="firstRowStripe" dxfId="459"/>
+      <tableStyleElement type="secondRowStripe" dxfId="458"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 13" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
-      <tableStyleElement type="headerRow" dxfId="461"/>
-      <tableStyleElement type="firstRowStripe" dxfId="460"/>
-      <tableStyleElement type="secondRowStripe" dxfId="459"/>
+      <tableStyleElement type="headerRow" dxfId="457"/>
+      <tableStyleElement type="firstRowStripe" dxfId="456"/>
+      <tableStyleElement type="secondRowStripe" dxfId="455"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 14" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
-      <tableStyleElement type="headerRow" dxfId="458"/>
-      <tableStyleElement type="firstRowStripe" dxfId="457"/>
-      <tableStyleElement type="secondRowStripe" dxfId="456"/>
+      <tableStyleElement type="headerRow" dxfId="454"/>
+      <tableStyleElement type="firstRowStripe" dxfId="453"/>
+      <tableStyleElement type="secondRowStripe" dxfId="452"/>
     </tableStyle>
     <tableStyle name="Hoja 1-style 15" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
-      <tableStyleElement type="headerRow" dxfId="455"/>
-      <tableStyleElement type="firstRowStripe" dxfId="454"/>
-      <tableStyleElement type="secondRowStripe" dxfId="453"/>
+      <tableStyleElement type="headerRow" dxfId="451"/>
+      <tableStyleElement type="firstRowStripe" dxfId="450"/>
+      <tableStyleElement type="secondRowStripe" dxfId="449"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -13815,56 +13688,56 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7AC742E-5CD0-4C3E-8385-35B49EC529DF}" name="Tabla5" displayName="Tabla5" ref="B4:O7" totalsRowShown="0" headerRowDxfId="452" dataDxfId="450" headerRowBorderDxfId="451" tableBorderDxfId="449" totalsRowBorderDxfId="448">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7AC742E-5CD0-4C3E-8385-35B49EC529DF}" name="Tabla5" displayName="Tabla5" ref="B4:O7" totalsRowShown="0" headerRowDxfId="448" dataDxfId="446" headerRowBorderDxfId="447" tableBorderDxfId="445" totalsRowBorderDxfId="444">
   <autoFilter ref="B4:O7" xr:uid="{E7AC742E-5CD0-4C3E-8385-35B49EC529DF}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{2CF4C360-077A-48D0-85F2-EF4C3E7E8359}" name="N.O Documento" dataDxfId="447"/>
-    <tableColumn id="2" xr3:uid="{4931D1BC-548D-454D-B25B-86679B18976E}" name="Tipo Documento" dataDxfId="446"/>
-    <tableColumn id="3" xr3:uid="{63BC7A1B-F698-470D-BFB5-5455F2CD10EB}" name="Contraseña" dataDxfId="445" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="16" xr3:uid="{1DE45D46-A423-49B0-ACAA-FF0755B96671}" name="Nombres" dataDxfId="444" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="4" xr3:uid="{F1BB3443-0948-41E4-99E7-4403909A9537}" name="Apellidos" dataDxfId="443"/>
-    <tableColumn id="5" xr3:uid="{ADA59EC9-264A-4411-8E30-B044251B0E18}" name="Correo1" dataDxfId="442" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="6" xr3:uid="{FD819F96-04D5-42E6-8AFC-8215AEBE268B}" name="Correo2" dataDxfId="441" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="7" xr3:uid="{96927A16-59D6-4DCB-BBF9-D44060E96A65}" name="Contacto1" dataDxfId="440"/>
-    <tableColumn id="10" xr3:uid="{A5DBB6BF-FDDD-40F4-8791-406904C9C5CE}" name="Fecha Nacimiento" dataDxfId="439"/>
-    <tableColumn id="11" xr3:uid="{92014813-04C5-4276-B452-60AA26A66627}" name="Foto" dataDxfId="438"/>
-    <tableColumn id="12" xr3:uid="{4F901097-370C-4E7B-A9A1-84289F6906BF}" name="Rol" dataDxfId="437"/>
-    <tableColumn id="13" xr3:uid="{2D33016D-BCC4-467E-887F-CA582318A9D9}" name="Curso" dataDxfId="436"/>
-    <tableColumn id="14" xr3:uid="{FD9911DB-158A-415F-8ADE-2A4E452E0166}" name="Grado" dataDxfId="435"/>
-    <tableColumn id="15" xr3:uid="{E4E628DA-6EA2-4DAA-9E8A-43751BAECBD0}" name="Jornada" dataDxfId="434"/>
+    <tableColumn id="1" xr3:uid="{2CF4C360-077A-48D0-85F2-EF4C3E7E8359}" name="N.O Documento" dataDxfId="443"/>
+    <tableColumn id="2" xr3:uid="{4931D1BC-548D-454D-B25B-86679B18976E}" name="Tipo Documento" dataDxfId="442"/>
+    <tableColumn id="3" xr3:uid="{63BC7A1B-F698-470D-BFB5-5455F2CD10EB}" name="Contraseña" dataDxfId="441" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="16" xr3:uid="{1DE45D46-A423-49B0-ACAA-FF0755B96671}" name="Nombres" dataDxfId="440" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="4" xr3:uid="{F1BB3443-0948-41E4-99E7-4403909A9537}" name="Apellidos" dataDxfId="439"/>
+    <tableColumn id="5" xr3:uid="{ADA59EC9-264A-4411-8E30-B044251B0E18}" name="Correo1" dataDxfId="438" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="6" xr3:uid="{FD819F96-04D5-42E6-8AFC-8215AEBE268B}" name="Correo2" dataDxfId="437" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="7" xr3:uid="{96927A16-59D6-4DCB-BBF9-D44060E96A65}" name="Contacto1" dataDxfId="436"/>
+    <tableColumn id="10" xr3:uid="{A5DBB6BF-FDDD-40F4-8791-406904C9C5CE}" name="Fecha Nacimiento" dataDxfId="435"/>
+    <tableColumn id="11" xr3:uid="{92014813-04C5-4276-B452-60AA26A66627}" name="Foto" dataDxfId="434"/>
+    <tableColumn id="12" xr3:uid="{4F901097-370C-4E7B-A9A1-84289F6906BF}" name="Rol" dataDxfId="433"/>
+    <tableColumn id="13" xr3:uid="{2D33016D-BCC4-467E-887F-CA582318A9D9}" name="Curso" dataDxfId="432"/>
+    <tableColumn id="14" xr3:uid="{FD9911DB-158A-415F-8ADE-2A4E452E0166}" name="Grado" dataDxfId="431"/>
+    <tableColumn id="15" xr3:uid="{E4E628DA-6EA2-4DAA-9E8A-43751BAECBD0}" name="Jornada" dataDxfId="430"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="90" xr:uid="{BBCEA42A-85FA-4A8D-B150-55464A19701D}" name="Tabla304645507791" displayName="Tabla304645507791" ref="E10:F13" totalsRowShown="0" headerRowDxfId="341" dataDxfId="339" headerRowBorderDxfId="340" tableBorderDxfId="338" totalsRowBorderDxfId="337">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="90" xr:uid="{BBCEA42A-85FA-4A8D-B150-55464A19701D}" name="Tabla304645507791" displayName="Tabla304645507791" ref="E10:F13" totalsRowShown="0" headerRowDxfId="337" dataDxfId="335" headerRowBorderDxfId="336" tableBorderDxfId="334" totalsRowBorderDxfId="333">
   <autoFilter ref="E10:F13" xr:uid="{BBCEA42A-85FA-4A8D-B150-55464A19701D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5FA143F0-FBD5-4EED-979B-62C30117E6C4}" name="ID Grado" dataDxfId="336"/>
-    <tableColumn id="2" xr3:uid="{2A06638D-F6B6-429C-9861-D2637E215AFB}" name="Grado" dataDxfId="335"/>
+    <tableColumn id="1" xr3:uid="{5FA143F0-FBD5-4EED-979B-62C30117E6C4}" name="ID Grado" dataDxfId="332"/>
+    <tableColumn id="2" xr3:uid="{2A06638D-F6B6-429C-9861-D2637E215AFB}" name="Grado" dataDxfId="331"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="92" xr:uid="{223B22DC-153B-4CB6-A92B-6D6837E1D41F}" name="Tabla284749537893" displayName="Tabla284749537893" ref="H10:I13" totalsRowShown="0" headerRowDxfId="334" dataDxfId="332" headerRowBorderDxfId="333" tableBorderDxfId="331" totalsRowBorderDxfId="330">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="92" xr:uid="{223B22DC-153B-4CB6-A92B-6D6837E1D41F}" name="Tabla284749537893" displayName="Tabla284749537893" ref="H10:I13" totalsRowShown="0" headerRowDxfId="330" dataDxfId="328" headerRowBorderDxfId="329" tableBorderDxfId="327" totalsRowBorderDxfId="326">
   <autoFilter ref="H10:I13" xr:uid="{223B22DC-153B-4CB6-A92B-6D6837E1D41F}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7C668C79-C86D-44A9-B642-189355F5D310}" name="ID Jornada" dataDxfId="329"/>
-    <tableColumn id="2" xr3:uid="{7B71F9CD-7562-4036-AED6-558E92FE43C0}" name="Jornada" dataDxfId="328"/>
+    <tableColumn id="1" xr3:uid="{7C668C79-C86D-44A9-B642-189355F5D310}" name="ID Jornada" dataDxfId="325"/>
+    <tableColumn id="2" xr3:uid="{7B71F9CD-7562-4036-AED6-558E92FE43C0}" name="Jornada" dataDxfId="324"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="93" xr:uid="{DD607BAB-4451-4CBF-8264-D534B50EC04D}" name="Tabla3440437094" displayName="Tabla3440437094" ref="K10:L14" totalsRowShown="0" headerRowDxfId="327" dataDxfId="325" headerRowBorderDxfId="326" tableBorderDxfId="324" totalsRowBorderDxfId="323">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="93" xr:uid="{DD607BAB-4451-4CBF-8264-D534B50EC04D}" name="Tabla3440437094" displayName="Tabla3440437094" ref="K10:L14" totalsRowShown="0" headerRowDxfId="323" dataDxfId="321" headerRowBorderDxfId="322" tableBorderDxfId="320" totalsRowBorderDxfId="319">
   <autoFilter ref="K10:L14" xr:uid="{DD607BAB-4451-4CBF-8264-D534B50EC04D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0B2B53BF-0C16-4B24-8ED0-166DBEE2C362}" name="ID Rol" dataDxfId="322"/>
-    <tableColumn id="2" xr3:uid="{4476D288-A412-483B-B897-1A335DCED585}" name="Rol" dataDxfId="321"/>
+    <tableColumn id="1" xr3:uid="{0B2B53BF-0C16-4B24-8ED0-166DBEE2C362}" name="ID Rol" dataDxfId="318"/>
+    <tableColumn id="2" xr3:uid="{4476D288-A412-483B-B897-1A335DCED585}" name="Rol" dataDxfId="317"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13874,11 +13747,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="94" xr:uid="{72E17C9F-B3AF-45AD-9FF3-32B99481320D}" name="Tabla94" displayName="Tabla94" ref="B24:F27" totalsRowShown="0">
   <autoFilter ref="B24:F27" xr:uid="{72E17C9F-B3AF-45AD-9FF3-32B99481320D}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{0F3272AF-700D-40F2-838F-38174468A628}" name="ID Anuncios" dataDxfId="320"/>
-    <tableColumn id="6" xr3:uid="{2D3D1933-6DA5-4FB9-A892-41D0D4E49480}" name="Titulo" dataDxfId="319"/>
-    <tableColumn id="2" xr3:uid="{32CAC941-08E9-4B3C-AAAE-DC21B289E13A}" name="Descripcion Anuncios" dataDxfId="318"/>
-    <tableColumn id="3" xr3:uid="{228FABCA-F33C-4F97-A7BE-CC918A40564F}" name="Archivo" dataDxfId="317"/>
-    <tableColumn id="4" xr3:uid="{6B7497C9-C266-462B-9C95-EF14648EF9F6}" name="Fecha" dataDxfId="316"/>
+    <tableColumn id="1" xr3:uid="{0F3272AF-700D-40F2-838F-38174468A628}" name="ID Anuncios" dataDxfId="316"/>
+    <tableColumn id="6" xr3:uid="{2D3D1933-6DA5-4FB9-A892-41D0D4E49480}" name="Titulo" dataDxfId="315"/>
+    <tableColumn id="2" xr3:uid="{32CAC941-08E9-4B3C-AAAE-DC21B289E13A}" name="Descripcion Anuncios" dataDxfId="314"/>
+    <tableColumn id="3" xr3:uid="{228FABCA-F33C-4F97-A7BE-CC918A40564F}" name="Archivo" dataDxfId="313"/>
+    <tableColumn id="4" xr3:uid="{6B7497C9-C266-462B-9C95-EF14648EF9F6}" name="Fecha" dataDxfId="312"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13888,194 +13761,194 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="95" xr:uid="{788C8C45-F567-4709-B746-E77540459625}" name="Tabla95" displayName="Tabla95" ref="H24:L27" totalsRowShown="0">
   <autoFilter ref="H24:L27" xr:uid="{788C8C45-F567-4709-B746-E77540459625}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{935B4DB5-EEC3-4C90-9D6D-931E921ADEB2}" name="ID Trabajos" dataDxfId="315"/>
-    <tableColumn id="2" xr3:uid="{9BFEE2C5-E35B-4624-8BF0-3BA2611B165B}" name="Titulo Trabajo" dataDxfId="314"/>
-    <tableColumn id="3" xr3:uid="{3162D276-AF15-4326-AFC3-DB1AD7E83273}" name="Descripcion Trabajos" dataDxfId="313"/>
-    <tableColumn id="4" xr3:uid="{0CCE52C4-F320-4C24-A15A-D74E92519664}" name="Archivo" dataDxfId="312"/>
-    <tableColumn id="5" xr3:uid="{66649D44-0D82-48E3-9E99-5AAE96270985}" name="Fecha Entrega" dataDxfId="311"/>
+    <tableColumn id="1" xr3:uid="{935B4DB5-EEC3-4C90-9D6D-931E921ADEB2}" name="ID Trabajos" dataDxfId="311"/>
+    <tableColumn id="2" xr3:uid="{9BFEE2C5-E35B-4624-8BF0-3BA2611B165B}" name="Titulo Trabajo" dataDxfId="310"/>
+    <tableColumn id="3" xr3:uid="{3162D276-AF15-4326-AFC3-DB1AD7E83273}" name="Descripcion Trabajos" dataDxfId="309"/>
+    <tableColumn id="4" xr3:uid="{0CCE52C4-F320-4C24-A15A-D74E92519664}" name="Archivo" dataDxfId="308"/>
+    <tableColumn id="5" xr3:uid="{66649D44-0D82-48E3-9E99-5AAE96270985}" name="Fecha Entrega" dataDxfId="307"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="97" xr:uid="{B79B76BF-DD91-4C42-8F6B-29EC8EF16922}" name="Tabla498" displayName="Tabla498" ref="N24:S27" totalsRowShown="0" headerRowDxfId="310" dataDxfId="308" headerRowBorderDxfId="309" tableBorderDxfId="307" totalsRowBorderDxfId="306">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="97" xr:uid="{B79B76BF-DD91-4C42-8F6B-29EC8EF16922}" name="Tabla498" displayName="Tabla498" ref="N24:S27" totalsRowShown="0" headerRowDxfId="306" dataDxfId="304" headerRowBorderDxfId="305" tableBorderDxfId="303" totalsRowBorderDxfId="302">
   <autoFilter ref="N24:S27" xr:uid="{B79B76BF-DD91-4C42-8F6B-29EC8EF16922}"/>
   <tableColumns count="6">
-    <tableColumn id="3" xr3:uid="{8FE5043E-55B8-44FD-A517-54AD32EB633D}" name="ID comentario" dataDxfId="305"/>
-    <tableColumn id="4" xr3:uid="{6137C372-4D52-4087-80F7-DD5D321DCD7B}" name="Descripcion" dataDxfId="304"/>
-    <tableColumn id="5" xr3:uid="{D16D4D60-539F-4BEF-B716-6DF55DB6B8BE}" name="Fecha" dataDxfId="303"/>
-    <tableColumn id="7" xr3:uid="{118C970B-968B-47D4-AE1D-166AA834CB4C}" name="ID Usuario" dataDxfId="302"/>
-    <tableColumn id="6" xr3:uid="{DD0E2FE1-DD32-4EE7-82A7-01B2DCFEBADE}" name="ID Anuncios" dataDxfId="301"/>
-    <tableColumn id="1" xr3:uid="{4497C3B7-350C-46B0-AA29-2FE06A19F6C4}" name="ID Trabajos" dataDxfId="300"/>
+    <tableColumn id="3" xr3:uid="{8FE5043E-55B8-44FD-A517-54AD32EB633D}" name="ID comentario" dataDxfId="301"/>
+    <tableColumn id="4" xr3:uid="{6137C372-4D52-4087-80F7-DD5D321DCD7B}" name="Descripcion" dataDxfId="300"/>
+    <tableColumn id="5" xr3:uid="{D16D4D60-539F-4BEF-B716-6DF55DB6B8BE}" name="Fecha" dataDxfId="299"/>
+    <tableColumn id="7" xr3:uid="{118C970B-968B-47D4-AE1D-166AA834CB4C}" name="ID Usuario" dataDxfId="298"/>
+    <tableColumn id="6" xr3:uid="{DD0E2FE1-DD32-4EE7-82A7-01B2DCFEBADE}" name="ID Anuncios" dataDxfId="297"/>
+    <tableColumn id="1" xr3:uid="{4497C3B7-350C-46B0-AA29-2FE06A19F6C4}" name="ID Trabajos" dataDxfId="296"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="98" xr:uid="{6CAA2C8E-8324-4325-A929-397F0FC6AD34}" name="Tabla699" displayName="Tabla699" ref="J17:O20" totalsRowShown="0" headerRowDxfId="299" dataDxfId="297" headerRowBorderDxfId="298" tableBorderDxfId="296">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="98" xr:uid="{6CAA2C8E-8324-4325-A929-397F0FC6AD34}" name="Tabla699" displayName="Tabla699" ref="J17:O20" totalsRowShown="0" headerRowDxfId="295" dataDxfId="293" headerRowBorderDxfId="294" tableBorderDxfId="292">
   <autoFilter ref="J17:O20" xr:uid="{6CAA2C8E-8324-4325-A929-397F0FC6AD34}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{B7B49C22-4F0F-4558-85DD-41BA17FB81C2}" name="ID entregados" dataDxfId="295"/>
-    <tableColumn id="2" xr3:uid="{42E6869F-8382-4099-A32B-8E1E06DC9815}" name="Archivo" dataDxfId="294"/>
-    <tableColumn id="3" xr3:uid="{9B59415E-666B-4882-8E62-3D239B866292}" name="Fecha Entrega" dataDxfId="293"/>
-    <tableColumn id="6" xr3:uid="{A59271DD-6531-4028-B729-756AFDAFABBA}" name="Nota" dataDxfId="292"/>
-    <tableColumn id="4" xr3:uid="{9EC1324E-EF14-48A2-8E0E-EBD0A31C35C0}" name="ID Usuario" dataDxfId="291"/>
-    <tableColumn id="5" xr3:uid="{4A1E947F-5C99-40A8-9C7A-212A39964130}" name="ID Trabajos" dataDxfId="290"/>
+    <tableColumn id="1" xr3:uid="{B7B49C22-4F0F-4558-85DD-41BA17FB81C2}" name="ID entregados" dataDxfId="291"/>
+    <tableColumn id="2" xr3:uid="{42E6869F-8382-4099-A32B-8E1E06DC9815}" name="Archivo" dataDxfId="290"/>
+    <tableColumn id="3" xr3:uid="{9B59415E-666B-4882-8E62-3D239B866292}" name="Fecha Entrega" dataDxfId="289"/>
+    <tableColumn id="6" xr3:uid="{A59271DD-6531-4028-B729-756AFDAFABBA}" name="Nota" dataDxfId="288"/>
+    <tableColumn id="4" xr3:uid="{9EC1324E-EF14-48A2-8E0E-EBD0A31C35C0}" name="ID Usuario" dataDxfId="287"/>
+    <tableColumn id="5" xr3:uid="{4A1E947F-5C99-40A8-9C7A-212A39964130}" name="ID Trabajos" dataDxfId="286"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="100" xr:uid="{5060941E-1162-428A-A2E9-444AAF70D817}" name="Tabla511101" displayName="Tabla511101" ref="B4:O7" totalsRowShown="0" headerRowDxfId="289" dataDxfId="287" headerRowBorderDxfId="288" tableBorderDxfId="286" totalsRowBorderDxfId="285">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="100" xr:uid="{5060941E-1162-428A-A2E9-444AAF70D817}" name="Tabla511101" displayName="Tabla511101" ref="B4:O7" totalsRowShown="0" headerRowDxfId="285" dataDxfId="283" headerRowBorderDxfId="284" tableBorderDxfId="282" totalsRowBorderDxfId="281">
   <autoFilter ref="B4:O7" xr:uid="{5060941E-1162-428A-A2E9-444AAF70D817}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{D02F79B1-F3CE-440C-845A-A314F341633F}" name="N.O Documento" dataDxfId="284"/>
-    <tableColumn id="2" xr3:uid="{6DBA977C-025E-4AEE-93D8-7D7C877443A9}" name="ID Tipo Documento" dataDxfId="283"/>
-    <tableColumn id="3" xr3:uid="{F03D46C3-5781-4791-B3C2-D40D68C64B8E}" name="Contraseña" dataDxfId="282" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="16" xr3:uid="{CB89B48C-FC41-449B-8CCC-DA348E514AE0}" name="Primer Nombre" dataDxfId="281" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="17" xr3:uid="{461A0CFA-EA70-45B1-AAB7-0259203299C7}" name="Segundo Nombre" dataDxfId="280"/>
-    <tableColumn id="4" xr3:uid="{BF20BB83-59DE-4867-ADD9-337B65CF9E14}" name="Primer Apellido" dataDxfId="279"/>
-    <tableColumn id="18" xr3:uid="{7F1FB2C2-E2C0-46CE-B70C-90E99A95174D}" name="Segundo Apellido" dataDxfId="278"/>
-    <tableColumn id="5" xr3:uid="{8F015393-4806-4462-8F0F-17CDDEA45CC9}" name="Correo1" dataDxfId="277" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="6" xr3:uid="{44229841-4D01-467A-85AA-E951F6BABED0}" name="Correo2" dataDxfId="276" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="7" xr3:uid="{8F7B2C60-62A9-40B0-8D91-591E1D456650}" name="Contacto1" dataDxfId="275"/>
-    <tableColumn id="19" xr3:uid="{440ED151-C831-4EE8-B936-DD69582A5E64}" name="Contacto2" dataDxfId="274"/>
-    <tableColumn id="10" xr3:uid="{EF441C89-64BA-4BD5-BD28-31F519094E51}" name="Fecha Nacimiento" dataDxfId="273"/>
-    <tableColumn id="11" xr3:uid="{CCEE270F-C77B-4D53-AC7B-EFEB427C5FD4}" name="Foto" dataDxfId="272"/>
-    <tableColumn id="12" xr3:uid="{944B6AA8-CC85-4518-90E2-F702175EE934}" name="ID Rol" dataDxfId="271"/>
+    <tableColumn id="1" xr3:uid="{D02F79B1-F3CE-440C-845A-A314F341633F}" name="N.O Documento" dataDxfId="280"/>
+    <tableColumn id="2" xr3:uid="{6DBA977C-025E-4AEE-93D8-7D7C877443A9}" name="ID Tipo Documento" dataDxfId="279"/>
+    <tableColumn id="3" xr3:uid="{F03D46C3-5781-4791-B3C2-D40D68C64B8E}" name="Contraseña" dataDxfId="278" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="16" xr3:uid="{CB89B48C-FC41-449B-8CCC-DA348E514AE0}" name="Primer Nombre" dataDxfId="277" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="17" xr3:uid="{461A0CFA-EA70-45B1-AAB7-0259203299C7}" name="Segundo Nombre" dataDxfId="276"/>
+    <tableColumn id="4" xr3:uid="{BF20BB83-59DE-4867-ADD9-337B65CF9E14}" name="Primer Apellido" dataDxfId="275"/>
+    <tableColumn id="18" xr3:uid="{7F1FB2C2-E2C0-46CE-B70C-90E99A95174D}" name="Segundo Apellido" dataDxfId="274"/>
+    <tableColumn id="5" xr3:uid="{8F015393-4806-4462-8F0F-17CDDEA45CC9}" name="Correo1" dataDxfId="273" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="6" xr3:uid="{44229841-4D01-467A-85AA-E951F6BABED0}" name="Correo2" dataDxfId="272" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="7" xr3:uid="{8F7B2C60-62A9-40B0-8D91-591E1D456650}" name="Contacto1" dataDxfId="271"/>
+    <tableColumn id="19" xr3:uid="{440ED151-C831-4EE8-B936-DD69582A5E64}" name="Contacto2" dataDxfId="270"/>
+    <tableColumn id="10" xr3:uid="{EF441C89-64BA-4BD5-BD28-31F519094E51}" name="Fecha Nacimiento" dataDxfId="269"/>
+    <tableColumn id="11" xr3:uid="{CCEE270F-C77B-4D53-AC7B-EFEB427C5FD4}" name="Foto" dataDxfId="268"/>
+    <tableColumn id="12" xr3:uid="{944B6AA8-CC85-4518-90E2-F702175EE934}" name="ID Rol" dataDxfId="267"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="101" xr:uid="{96F826A9-125A-402B-8294-7BD6C4B2585A}" name="Tabla2739424471102" displayName="Tabla2739424471102" ref="B11:C14" totalsRowShown="0" headerRowDxfId="270" dataDxfId="268" headerRowBorderDxfId="269" tableBorderDxfId="267" totalsRowBorderDxfId="266">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="101" xr:uid="{96F826A9-125A-402B-8294-7BD6C4B2585A}" name="Tabla2739424471102" displayName="Tabla2739424471102" ref="B11:C14" totalsRowShown="0" headerRowDxfId="266" dataDxfId="264" headerRowBorderDxfId="265" tableBorderDxfId="263" totalsRowBorderDxfId="262">
   <autoFilter ref="B11:C14" xr:uid="{96F826A9-125A-402B-8294-7BD6C4B2585A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B4D3AFDF-A970-4553-8393-12C5C04B78E3}" name="ID Tipo Documento" dataDxfId="265"/>
-    <tableColumn id="2" xr3:uid="{6C7D2623-5304-4579-ABA6-142CD646C445}" name="Tipo Documento" dataDxfId="264"/>
+    <tableColumn id="1" xr3:uid="{B4D3AFDF-A970-4553-8393-12C5C04B78E3}" name="ID Tipo Documento" dataDxfId="261"/>
+    <tableColumn id="2" xr3:uid="{6C7D2623-5304-4579-ABA6-142CD646C445}" name="Tipo Documento" dataDxfId="260"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="106" xr:uid="{6AFC29F1-F786-4DAE-882B-704F8ED9CCDC}" name="Tabla294169107" displayName="Tabla294169107" ref="E11:H14" totalsRowShown="0" headerRowDxfId="263" dataDxfId="261" headerRowBorderDxfId="262" tableBorderDxfId="260" totalsRowBorderDxfId="259">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="106" xr:uid="{6AFC29F1-F786-4DAE-882B-704F8ED9CCDC}" name="Tabla294169107" displayName="Tabla294169107" ref="E11:H14" totalsRowShown="0" headerRowDxfId="259" dataDxfId="257" headerRowBorderDxfId="258" tableBorderDxfId="256" totalsRowBorderDxfId="255">
   <autoFilter ref="E11:H14" xr:uid="{6AFC29F1-F786-4DAE-882B-704F8ED9CCDC}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E2595A0A-7D25-43D9-9493-AC883901BFE0}" name="ID Curso" dataDxfId="258"/>
-    <tableColumn id="2" xr3:uid="{6BB9DE1E-1F03-4D21-9D24-9FA9C2105989}" name="Nombre Curso" dataDxfId="257"/>
-    <tableColumn id="4" xr3:uid="{984CD5B1-4857-4947-8EFE-F190AED98316}" name="ID Jornada" dataDxfId="256"/>
-    <tableColumn id="5" xr3:uid="{30751D2F-E471-4BC9-80EA-A089A5396428}" name="ID Grado" dataDxfId="255"/>
+    <tableColumn id="1" xr3:uid="{E2595A0A-7D25-43D9-9493-AC883901BFE0}" name="ID Curso" dataDxfId="254"/>
+    <tableColumn id="2" xr3:uid="{6BB9DE1E-1F03-4D21-9D24-9FA9C2105989}" name="Nombre Curso" dataDxfId="253"/>
+    <tableColumn id="4" xr3:uid="{984CD5B1-4857-4947-8EFE-F190AED98316}" name="ID Jornada" dataDxfId="252"/>
+    <tableColumn id="5" xr3:uid="{30751D2F-E471-4BC9-80EA-A089A5396428}" name="ID Grado" dataDxfId="251"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{8C2BDD3F-BF41-4237-AF1C-636268541A14}" name="Tabla7" displayName="Tabla7" ref="B11:K14" totalsRowShown="0" headerRowDxfId="433" dataDxfId="432">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{8C2BDD3F-BF41-4237-AF1C-636268541A14}" name="Tabla7" displayName="Tabla7" ref="B11:K14" totalsRowShown="0" headerRowDxfId="429" dataDxfId="428">
   <autoFilter ref="B11:K14" xr:uid="{8C2BDD3F-BF41-4237-AF1C-636268541A14}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{8F36C77E-27B8-4C49-AA81-76866AE781DA}" name="Nombre Aula" dataDxfId="431"/>
-    <tableColumn id="2" xr3:uid="{FF651E2D-BA21-4591-80DF-ED69BA4F201D}" name="Nombre Materia" dataDxfId="430"/>
-    <tableColumn id="3" xr3:uid="{CFF3B4AC-B8FD-4FD5-8F4E-4FBD010AC52A}" name="Profesor" dataDxfId="429"/>
-    <tableColumn id="4" xr3:uid="{97B6F6D0-65C4-4728-8B00-B68D4C16F67B}" name="Curso" dataDxfId="428"/>
-    <tableColumn id="10" xr3:uid="{F16DDE4D-212B-45A8-A084-3663773CF98A}" name="Alumno" dataDxfId="427"/>
-    <tableColumn id="5" xr3:uid="{6A94C8A3-14B7-4916-9C83-2EB782BA2BC7}" name="Anuncios" dataDxfId="426"/>
-    <tableColumn id="6" xr3:uid="{53E9D3F1-C540-40AF-89A0-7F89EDE2D037}" name="Trabajos" dataDxfId="425"/>
-    <tableColumn id="7" xr3:uid="{A3981DE0-E15E-4729-9CAA-0899D441F0B5}" name="Comentario" dataDxfId="424"/>
-    <tableColumn id="8" xr3:uid="{B825E506-A09D-47B3-A848-C800E9EC7256}" name="Trabajo Entregado" dataDxfId="423"/>
-    <tableColumn id="9" xr3:uid="{C385F82E-07A9-4C94-8749-4B942BAB4D10}" name="Nota" dataDxfId="422"/>
+    <tableColumn id="1" xr3:uid="{8F36C77E-27B8-4C49-AA81-76866AE781DA}" name="Nombre Aula" dataDxfId="427"/>
+    <tableColumn id="2" xr3:uid="{FF651E2D-BA21-4591-80DF-ED69BA4F201D}" name="Nombre Materia" dataDxfId="426"/>
+    <tableColumn id="3" xr3:uid="{CFF3B4AC-B8FD-4FD5-8F4E-4FBD010AC52A}" name="Profesor" dataDxfId="425"/>
+    <tableColumn id="4" xr3:uid="{97B6F6D0-65C4-4728-8B00-B68D4C16F67B}" name="Curso" dataDxfId="424"/>
+    <tableColumn id="10" xr3:uid="{F16DDE4D-212B-45A8-A084-3663773CF98A}" name="Alumno" dataDxfId="423"/>
+    <tableColumn id="5" xr3:uid="{6A94C8A3-14B7-4916-9C83-2EB782BA2BC7}" name="Anuncios" dataDxfId="422"/>
+    <tableColumn id="6" xr3:uid="{53E9D3F1-C540-40AF-89A0-7F89EDE2D037}" name="Trabajos" dataDxfId="421"/>
+    <tableColumn id="7" xr3:uid="{A3981DE0-E15E-4729-9CAA-0899D441F0B5}" name="Comentario" dataDxfId="420"/>
+    <tableColumn id="8" xr3:uid="{B825E506-A09D-47B3-A848-C800E9EC7256}" name="Trabajo Entregado" dataDxfId="419"/>
+    <tableColumn id="9" xr3:uid="{C385F82E-07A9-4C94-8749-4B942BAB4D10}" name="Nota" dataDxfId="418"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="107" xr:uid="{FA5780ED-E3E2-4440-B85D-AF7EE1910729}" name="Tabla304645507791108" displayName="Tabla304645507791108" ref="J11:L14" totalsRowShown="0" headerRowDxfId="254" dataDxfId="252" headerRowBorderDxfId="253" tableBorderDxfId="251" totalsRowBorderDxfId="250">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="107" xr:uid="{FA5780ED-E3E2-4440-B85D-AF7EE1910729}" name="Tabla304645507791108" displayName="Tabla304645507791108" ref="J11:L14" totalsRowShown="0" headerRowDxfId="250" dataDxfId="248" headerRowBorderDxfId="249" tableBorderDxfId="247" totalsRowBorderDxfId="246">
   <autoFilter ref="J11:L14" xr:uid="{FA5780ED-E3E2-4440-B85D-AF7EE1910729}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{862BDD31-074D-4D57-B708-753617D715CB}" name="ID Grado" dataDxfId="249"/>
-    <tableColumn id="2" xr3:uid="{DDCF964C-EC22-428F-915F-C039BDBBC417}" name="Grado" dataDxfId="248"/>
-    <tableColumn id="3" xr3:uid="{B06AAE1E-89DD-400B-B2D6-7EEBE7EAC2BC}" name="Descripcion" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{862BDD31-074D-4D57-B708-753617D715CB}" name="ID Grado" dataDxfId="245"/>
+    <tableColumn id="2" xr3:uid="{DDCF964C-EC22-428F-915F-C039BDBBC417}" name="Grado" dataDxfId="244"/>
+    <tableColumn id="3" xr3:uid="{B06AAE1E-89DD-400B-B2D6-7EEBE7EAC2BC}" name="Descripcion" dataDxfId="243"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="108" xr:uid="{DA57B9DC-92DD-4AC7-A195-38CD05C19C53}" name="Tabla284749537893109" displayName="Tabla284749537893109" ref="N11:P14" totalsRowShown="0" headerRowDxfId="247" dataDxfId="245" headerRowBorderDxfId="246" tableBorderDxfId="244" totalsRowBorderDxfId="243">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="108" xr:uid="{DA57B9DC-92DD-4AC7-A195-38CD05C19C53}" name="Tabla284749537893109" displayName="Tabla284749537893109" ref="N11:P14" totalsRowShown="0" headerRowDxfId="242" dataDxfId="240" headerRowBorderDxfId="241" tableBorderDxfId="239" totalsRowBorderDxfId="238">
   <autoFilter ref="N11:P14" xr:uid="{DA57B9DC-92DD-4AC7-A195-38CD05C19C53}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7FEE83A0-A5C5-47CD-8E6C-C292A6D89EB0}" name="ID Jornada" dataDxfId="242"/>
-    <tableColumn id="2" xr3:uid="{E1FB670E-D985-404C-8291-D10E7A9FA292}" name="Jornada" dataDxfId="241"/>
-    <tableColumn id="3" xr3:uid="{C170F7E4-C8D2-4D7D-A8AC-8586A1CF6800}" name="Descripcion" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{7FEE83A0-A5C5-47CD-8E6C-C292A6D89EB0}" name="ID Jornada" dataDxfId="237"/>
+    <tableColumn id="2" xr3:uid="{E1FB670E-D985-404C-8291-D10E7A9FA292}" name="Jornada" dataDxfId="236"/>
+    <tableColumn id="3" xr3:uid="{C170F7E4-C8D2-4D7D-A8AC-8586A1CF6800}" name="Descripcion" dataDxfId="235"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="109" xr:uid="{6F50273C-5B06-49A3-A04D-115455B03FC0}" name="Tabla3440437094110" displayName="Tabla3440437094110" ref="R11:S15" totalsRowShown="0" headerRowDxfId="240" dataDxfId="238" headerRowBorderDxfId="239" tableBorderDxfId="237" totalsRowBorderDxfId="236">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="109" xr:uid="{6F50273C-5B06-49A3-A04D-115455B03FC0}" name="Tabla3440437094110" displayName="Tabla3440437094110" ref="R11:S15" totalsRowShown="0" headerRowDxfId="234" dataDxfId="232" headerRowBorderDxfId="233" tableBorderDxfId="231" totalsRowBorderDxfId="230">
   <autoFilter ref="R11:S15" xr:uid="{6F50273C-5B06-49A3-A04D-115455B03FC0}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E2E6A769-7D84-4A8C-88BA-3A137FBFB78E}" name="ID Rol" dataDxfId="235"/>
-    <tableColumn id="2" xr3:uid="{B8AB7960-EA85-4152-B663-220085D70A4E}" name="Rol" dataDxfId="234"/>
+    <tableColumn id="1" xr3:uid="{E2E6A769-7D84-4A8C-88BA-3A137FBFB78E}" name="ID Rol" dataDxfId="229"/>
+    <tableColumn id="2" xr3:uid="{B8AB7960-EA85-4152-B663-220085D70A4E}" name="Rol" dataDxfId="228"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="111" xr:uid="{BE369BB5-2313-49C1-AE4E-721B3E8B5017}" name="Tabla445675112" displayName="Tabla445675112" ref="Q4:R7" totalsRowShown="0" headerRowDxfId="233" dataDxfId="231" headerRowBorderDxfId="232" tableBorderDxfId="230" totalsRowBorderDxfId="229">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="111" xr:uid="{BE369BB5-2313-49C1-AE4E-721B3E8B5017}" name="Tabla445675112" displayName="Tabla445675112" ref="Q4:R7" totalsRowShown="0" headerRowDxfId="227" dataDxfId="225" headerRowBorderDxfId="226" tableBorderDxfId="224" totalsRowBorderDxfId="223">
   <autoFilter ref="Q4:R7" xr:uid="{BE369BB5-2313-49C1-AE4E-721B3E8B5017}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2A00B0B5-AC7C-4C96-B36C-60F98A01BC3A}" name="ID Curso" dataDxfId="228"/>
-    <tableColumn id="2" xr3:uid="{9AD20A45-BA3E-4481-B588-8D8128F45F09}" name="ID Usuarios" dataDxfId="227"/>
+    <tableColumn id="1" xr3:uid="{2A00B0B5-AC7C-4C96-B36C-60F98A01BC3A}" name="ID Curso" dataDxfId="222"/>
+    <tableColumn id="2" xr3:uid="{9AD20A45-BA3E-4481-B588-8D8128F45F09}" name="ID Usuarios" dataDxfId="221"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="112" xr:uid="{55D91AD9-4F03-4F28-B743-376E8454B15C}" name="Tabla813113" displayName="Tabla813113" ref="B18:G21" totalsRowShown="0" headerRowDxfId="226" dataDxfId="225">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="112" xr:uid="{55D91AD9-4F03-4F28-B743-376E8454B15C}" name="Tabla813113" displayName="Tabla813113" ref="B18:G21" totalsRowShown="0" headerRowDxfId="220" dataDxfId="219">
   <autoFilter ref="B18:G21" xr:uid="{55D91AD9-4F03-4F28-B743-376E8454B15C}"/>
   <tableColumns count="6">
-    <tableColumn id="6" xr3:uid="{47614192-FF26-4DF2-8D7D-7A76B4A19AAB}" name="ID Horario" dataDxfId="224"/>
-    <tableColumn id="1" xr3:uid="{1ABC6D19-A95A-4C6C-A4F7-76A9137736BC}" name="Titulo Horario" dataDxfId="223"/>
-    <tableColumn id="2" xr3:uid="{C1D8A097-59F0-4E64-8154-7D89B53C571C}" name="Imagen Horario" dataDxfId="222"/>
-    <tableColumn id="3" xr3:uid="{642381B9-7E28-4EAC-9281-0A7AC96BC49E}" name="Descripcion" dataDxfId="221"/>
-    <tableColumn id="4" xr3:uid="{99F58ADF-C09A-4768-92DE-5CFCCD935283}" name="Curso" dataDxfId="220"/>
-    <tableColumn id="5" xr3:uid="{5B4552A2-57E6-41DB-88C9-6FF5D5812AEF}" name="ID Profesor" dataDxfId="219"/>
+    <tableColumn id="6" xr3:uid="{47614192-FF26-4DF2-8D7D-7A76B4A19AAB}" name="ID Horario" dataDxfId="218"/>
+    <tableColumn id="1" xr3:uid="{1ABC6D19-A95A-4C6C-A4F7-76A9137736BC}" name="Titulo Horario" dataDxfId="217"/>
+    <tableColumn id="2" xr3:uid="{C1D8A097-59F0-4E64-8154-7D89B53C571C}" name="Imagen Horario" dataDxfId="216"/>
+    <tableColumn id="3" xr3:uid="{642381B9-7E28-4EAC-9281-0A7AC96BC49E}" name="Descripcion" dataDxfId="215"/>
+    <tableColumn id="4" xr3:uid="{99F58ADF-C09A-4768-92DE-5CFCCD935283}" name="Curso" dataDxfId="214"/>
+    <tableColumn id="5" xr3:uid="{5B4552A2-57E6-41DB-88C9-6FF5D5812AEF}" name="ID Profesor" dataDxfId="213"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="113" xr:uid="{0391CE60-4033-4537-BDDF-CE0B8EAF1519}" name="Tabla712114" displayName="Tabla712114" ref="B25:F28" totalsRowShown="0" headerRowDxfId="218" dataDxfId="217">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="113" xr:uid="{0391CE60-4033-4537-BDDF-CE0B8EAF1519}" name="Tabla712114" displayName="Tabla712114" ref="B25:F28" totalsRowShown="0" headerRowDxfId="212" dataDxfId="211">
   <autoFilter ref="B25:F28" xr:uid="{0391CE60-4033-4537-BDDF-CE0B8EAF1519}"/>
   <tableColumns count="5">
-    <tableColumn id="26" xr3:uid="{77176C6E-FF74-4F1D-A91E-BF6C0C901464}" name="ID Aula" dataDxfId="216"/>
-    <tableColumn id="1" xr3:uid="{A34AA7AA-DCEA-4586-9D66-E9C9A5CF4A08}" name="Nombre Aula" dataDxfId="215"/>
-    <tableColumn id="2" xr3:uid="{6BCAA4B1-0BEB-4070-9023-9BECAC0240D8}" name="ID Materia" dataDxfId="214"/>
-    <tableColumn id="3" xr3:uid="{AD57CE43-40C7-4F8A-B858-099A7492A41E}" name="Profesor" dataDxfId="213"/>
-    <tableColumn id="4" xr3:uid="{5FA5F869-2758-4C5C-A93E-76DDE3F6F05D}" name="Curso" dataDxfId="212"/>
+    <tableColumn id="26" xr3:uid="{77176C6E-FF74-4F1D-A91E-BF6C0C901464}" name="ID Aula" dataDxfId="210"/>
+    <tableColumn id="1" xr3:uid="{A34AA7AA-DCEA-4586-9D66-E9C9A5CF4A08}" name="Nombre Aula" dataDxfId="209"/>
+    <tableColumn id="2" xr3:uid="{6BCAA4B1-0BEB-4070-9023-9BECAC0240D8}" name="ID Materia" dataDxfId="208"/>
+    <tableColumn id="3" xr3:uid="{AD57CE43-40C7-4F8A-B858-099A7492A41E}" name="Profesor" dataDxfId="207"/>
+    <tableColumn id="4" xr3:uid="{5FA5F869-2758-4C5C-A93E-76DDE3F6F05D}" name="Curso" dataDxfId="206"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="114" xr:uid="{5E1CA139-BBA4-4E67-B3D6-4EDA817A9C11}" name="Tabla356576115" displayName="Tabla356576115" ref="I18:K21" totalsRowShown="0" headerRowDxfId="211" dataDxfId="209" headerRowBorderDxfId="210" tableBorderDxfId="208" totalsRowBorderDxfId="207">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="114" xr:uid="{5E1CA139-BBA4-4E67-B3D6-4EDA817A9C11}" name="Tabla356576115" displayName="Tabla356576115" ref="I18:K21" totalsRowShown="0" headerRowDxfId="205" dataDxfId="203" headerRowBorderDxfId="204" tableBorderDxfId="202" totalsRowBorderDxfId="201">
   <autoFilter ref="I18:K21" xr:uid="{5E1CA139-BBA4-4E67-B3D6-4EDA817A9C11}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B3A4A961-3B2E-48C1-A6D1-A3EAE415F0D2}" name="ID Materia" dataDxfId="206"/>
-    <tableColumn id="2" xr3:uid="{6F61C203-5224-4FA6-8917-2CA7D5751B11}" name="Nombre Materia" dataDxfId="205"/>
-    <tableColumn id="3" xr3:uid="{4CD26D76-2BBC-46FD-AF1E-2C75D6F8C50C}" name="Descripcion" dataDxfId="204"/>
+    <tableColumn id="1" xr3:uid="{B3A4A961-3B2E-48C1-A6D1-A3EAE415F0D2}" name="ID Materia" dataDxfId="200"/>
+    <tableColumn id="2" xr3:uid="{6F61C203-5224-4FA6-8917-2CA7D5751B11}" name="Nombre Materia" dataDxfId="199"/>
+    <tableColumn id="3" xr3:uid="{4CD26D76-2BBC-46FD-AF1E-2C75D6F8C50C}" name="Descripcion" dataDxfId="198"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14085,252 +13958,250 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="115" xr:uid="{FD592122-3947-4ECC-BC98-E6BEC5688EDD}" name="Tabla94116" displayName="Tabla94116" ref="H25:N28" totalsRowShown="0">
   <autoFilter ref="H25:N28" xr:uid="{FD592122-3947-4ECC-BC98-E6BEC5688EDD}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E8951B68-2303-4CA9-B205-C8FD06346AA3}" name="ID Anuncios" dataDxfId="203"/>
-    <tableColumn id="6" xr3:uid="{0549C447-86B7-4FAB-9457-E186EF02B45E}" name="Titulo" dataDxfId="202"/>
-    <tableColumn id="2" xr3:uid="{A628A612-7276-4AB4-B76C-C578EF8CF5FB}" name="Descripcion Anuncios" dataDxfId="201"/>
-    <tableColumn id="3" xr3:uid="{790A699E-3D35-44FD-B866-F9E8B2124E0E}" name="Archivo" dataDxfId="200"/>
-    <tableColumn id="4" xr3:uid="{F90E5BC0-E6FD-46E6-A178-604DD7D738E9}" name="Fecha" dataDxfId="199"/>
-    <tableColumn id="7" xr3:uid="{2B52EFB2-6089-4575-AC6C-D91CB261C85B}" name="ID Aula" dataDxfId="198"/>
-    <tableColumn id="8" xr3:uid="{CDDFC040-5D57-4B98-AE26-83E324E07EB3}" name="ID Usuario" dataDxfId="197"/>
+    <tableColumn id="1" xr3:uid="{E8951B68-2303-4CA9-B205-C8FD06346AA3}" name="ID Anuncios" dataDxfId="197"/>
+    <tableColumn id="6" xr3:uid="{0549C447-86B7-4FAB-9457-E186EF02B45E}" name="Titulo" dataDxfId="196"/>
+    <tableColumn id="2" xr3:uid="{A628A612-7276-4AB4-B76C-C578EF8CF5FB}" name="Descripcion Anuncios" dataDxfId="195"/>
+    <tableColumn id="3" xr3:uid="{790A699E-3D35-44FD-B866-F9E8B2124E0E}" name="Archivo" dataDxfId="194"/>
+    <tableColumn id="4" xr3:uid="{F90E5BC0-E6FD-46E6-A178-604DD7D738E9}" name="Fecha" dataDxfId="193"/>
+    <tableColumn id="7" xr3:uid="{2B52EFB2-6089-4575-AC6C-D91CB261C85B}" name="ID Aula" dataDxfId="192"/>
+    <tableColumn id="8" xr3:uid="{CDDFC040-5D57-4B98-AE26-83E324E07EB3}" name="ID Usuario" dataDxfId="191"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="116" xr:uid="{880FB7CA-779A-498E-8F82-CEF190178801}" name="Tabla95117" displayName="Tabla95117" ref="B32:G35" totalsRowShown="0">
-  <autoFilter ref="B32:G35" xr:uid="{880FB7CA-779A-498E-8F82-CEF190178801}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1726CC30-98C5-4C10-9E26-AA7641ACC27A}" name="ID Trabajos" dataDxfId="196"/>
-    <tableColumn id="2" xr3:uid="{49877BD2-88A6-4B5A-A3DC-C7AA7EA9C12B}" name="Titulo Trabajo" dataDxfId="195"/>
-    <tableColumn id="3" xr3:uid="{C2A0493D-84F2-4DDE-B83B-0995497F31BC}" name="Descripcion Trabajos" dataDxfId="194"/>
-    <tableColumn id="4" xr3:uid="{8BCF9406-1442-405A-99BF-B0ECBEBA7CF1}" name="Archivo" dataDxfId="193"/>
-    <tableColumn id="5" xr3:uid="{F6A88E0D-703B-4D84-A095-48916815AC59}" name="Fecha Entrega" dataDxfId="192"/>
-    <tableColumn id="9" xr3:uid="{F789171E-338E-473F-BFA0-F7E2CAED56A6}" name="ID Aula" dataDxfId="191"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="116" xr:uid="{880FB7CA-779A-498E-8F82-CEF190178801}" name="Tabla95117" displayName="Tabla95117" ref="B32:F35" totalsRowShown="0">
+  <autoFilter ref="B32:F35" xr:uid="{880FB7CA-779A-498E-8F82-CEF190178801}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{1726CC30-98C5-4C10-9E26-AA7641ACC27A}" name="ID Trabajos" dataDxfId="190"/>
+    <tableColumn id="2" xr3:uid="{49877BD2-88A6-4B5A-A3DC-C7AA7EA9C12B}" name="Titulo Trabajo" dataDxfId="189"/>
+    <tableColumn id="3" xr3:uid="{C2A0493D-84F2-4DDE-B83B-0995497F31BC}" name="Descripcion Trabajos" dataDxfId="188"/>
+    <tableColumn id="5" xr3:uid="{F6A88E0D-703B-4D84-A095-48916815AC59}" name="Fecha Entrega" dataDxfId="187"/>
+    <tableColumn id="9" xr3:uid="{F789171E-338E-473F-BFA0-F7E2CAED56A6}" name="ID Aula" dataDxfId="186"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="117" xr:uid="{6332F8B1-622B-404B-AAB5-81232D7A9F73}" name="Tabla498118" displayName="Tabla498118" ref="I32:N35" totalsRowShown="0" headerRowDxfId="190" dataDxfId="188" headerRowBorderDxfId="189" tableBorderDxfId="187" totalsRowBorderDxfId="186">
-  <autoFilter ref="I32:N35" xr:uid="{6332F8B1-622B-404B-AAB5-81232D7A9F73}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="117" xr:uid="{6332F8B1-622B-404B-AAB5-81232D7A9F73}" name="Tabla498118" displayName="Tabla498118" ref="H32:M35" totalsRowShown="0" headerRowDxfId="185" dataDxfId="183" headerRowBorderDxfId="184" tableBorderDxfId="182" totalsRowBorderDxfId="181">
+  <autoFilter ref="H32:M35" xr:uid="{6332F8B1-622B-404B-AAB5-81232D7A9F73}"/>
   <tableColumns count="6">
-    <tableColumn id="3" xr3:uid="{6C834D1C-ABF0-44A9-8CA0-37E934D19A61}" name="ID comentario" dataDxfId="185"/>
-    <tableColumn id="4" xr3:uid="{19DB6412-1ABB-4D48-B824-B5DE9781B731}" name="Descripcion" dataDxfId="184"/>
-    <tableColumn id="5" xr3:uid="{07D2A797-CDA9-4E78-8C74-2A5D7C6E533F}" name="Fecha" dataDxfId="183"/>
-    <tableColumn id="7" xr3:uid="{28EBB91B-B5D7-4D79-BB6A-36CEB2BCE440}" name="ID Usuario" dataDxfId="182"/>
-    <tableColumn id="6" xr3:uid="{F4A4E13A-CEAB-47F6-99CA-2BD058026CED}" name="ID Anuncios" dataDxfId="181"/>
-    <tableColumn id="1" xr3:uid="{B70DBF1A-5B78-4067-A46F-BC077A88333B}" name="ID Trabajos" dataDxfId="180"/>
+    <tableColumn id="3" xr3:uid="{6C834D1C-ABF0-44A9-8CA0-37E934D19A61}" name="ID comentario" dataDxfId="180"/>
+    <tableColumn id="4" xr3:uid="{19DB6412-1ABB-4D48-B824-B5DE9781B731}" name="Descripcion" dataDxfId="179"/>
+    <tableColumn id="5" xr3:uid="{07D2A797-CDA9-4E78-8C74-2A5D7C6E533F}" name="Fecha" dataDxfId="178"/>
+    <tableColumn id="7" xr3:uid="{28EBB91B-B5D7-4D79-BB6A-36CEB2BCE440}" name="ID Usuario" dataDxfId="177"/>
+    <tableColumn id="6" xr3:uid="{F4A4E13A-CEAB-47F6-99CA-2BD058026CED}" name="ID Anuncios" dataDxfId="176"/>
+    <tableColumn id="1" xr3:uid="{B70DBF1A-5B78-4067-A46F-BC077A88333B}" name="ID Trabajos" dataDxfId="175"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D291AABB-C156-41AD-B5F8-EF37E1E0F148}" name="Tabla8" displayName="Tabla8" ref="B18:F21" totalsRowShown="0" headerRowDxfId="421" dataDxfId="420">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D291AABB-C156-41AD-B5F8-EF37E1E0F148}" name="Tabla8" displayName="Tabla8" ref="B18:F21" totalsRowShown="0" headerRowDxfId="417" dataDxfId="416">
   <autoFilter ref="B18:F21" xr:uid="{D291AABB-C156-41AD-B5F8-EF37E1E0F148}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{96D9407A-2609-47F3-9BD8-D7CC5BD31D37}" name="Titulo Horario" dataDxfId="419"/>
-    <tableColumn id="2" xr3:uid="{51CF7BC8-35A8-4FE0-8E55-A331684285E0}" name="Imagen Horario" dataDxfId="418"/>
-    <tableColumn id="3" xr3:uid="{781F7FFE-026E-4868-9AEE-A231EEF0CE6B}" name="Descripcion" dataDxfId="417"/>
-    <tableColumn id="4" xr3:uid="{5E29E7A8-CAC9-4165-AF37-75AE6FFC9FF1}" name="Curso" dataDxfId="416"/>
-    <tableColumn id="5" xr3:uid="{395D8B41-B946-46A4-9A00-1290C13E0A18}" name="ID Profesor" dataDxfId="415"/>
+    <tableColumn id="1" xr3:uid="{96D9407A-2609-47F3-9BD8-D7CC5BD31D37}" name="Titulo Horario" dataDxfId="415"/>
+    <tableColumn id="2" xr3:uid="{51CF7BC8-35A8-4FE0-8E55-A331684285E0}" name="Imagen Horario" dataDxfId="414"/>
+    <tableColumn id="3" xr3:uid="{781F7FFE-026E-4868-9AEE-A231EEF0CE6B}" name="Descripcion" dataDxfId="413"/>
+    <tableColumn id="4" xr3:uid="{5E29E7A8-CAC9-4165-AF37-75AE6FFC9FF1}" name="Curso" dataDxfId="412"/>
+    <tableColumn id="5" xr3:uid="{395D8B41-B946-46A4-9A00-1290C13E0A18}" name="ID Profesor" dataDxfId="411"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="118" xr:uid="{4382CBAB-F3D6-47DB-B226-67050DE66316}" name="Tabla699119" displayName="Tabla699119" ref="B39:G42" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
-  <autoFilter ref="B39:G42" xr:uid="{4382CBAB-F3D6-47DB-B226-67050DE66316}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D81D39F0-E9EB-4E09-9D98-D431DBDFF341}" name="ID entregados" dataDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{2827E31A-7936-4286-B07E-C61A6522BBE6}" name="Archivo" dataDxfId="174"/>
-    <tableColumn id="3" xr3:uid="{454AEC47-1A69-4A03-BDCC-7BCDB9B728D6}" name="Fecha Entrega" dataDxfId="173"/>
-    <tableColumn id="6" xr3:uid="{CECA93B4-AACE-45E1-AC96-48723C3E7049}" name="Nota" dataDxfId="172"/>
-    <tableColumn id="4" xr3:uid="{1455B5A5-8E64-4859-AE05-5F2F8FFF3A16}" name="ID Usuario" dataDxfId="171"/>
-    <tableColumn id="5" xr3:uid="{D1CB2C89-8F68-4053-A567-FD62A646333F}" name="ID Trabajos" dataDxfId="170"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="118" xr:uid="{4382CBAB-F3D6-47DB-B226-67050DE66316}" name="Tabla699119" displayName="Tabla699119" ref="B39:F42" totalsRowShown="0" headerRowDxfId="174" dataDxfId="172" headerRowBorderDxfId="173" tableBorderDxfId="171">
+  <autoFilter ref="B39:F42" xr:uid="{4382CBAB-F3D6-47DB-B226-67050DE66316}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D81D39F0-E9EB-4E09-9D98-D431DBDFF341}" name="ID entregados" dataDxfId="170"/>
+    <tableColumn id="3" xr3:uid="{454AEC47-1A69-4A03-BDCC-7BCDB9B728D6}" name="Fecha Entrega" dataDxfId="169"/>
+    <tableColumn id="6" xr3:uid="{CECA93B4-AACE-45E1-AC96-48723C3E7049}" name="Nota" dataDxfId="168"/>
+    <tableColumn id="4" xr3:uid="{1455B5A5-8E64-4859-AE05-5F2F8FFF3A16}" name="ID Usuario" dataDxfId="167"/>
+    <tableColumn id="5" xr3:uid="{D1CB2C89-8F68-4053-A567-FD62A646333F}" name="ID Trabajos" dataDxfId="166"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="119" xr:uid="{7AB81B42-CAF1-425D-A49A-BB0B3891506C}" name="Tabla1927668614120" displayName="Tabla1927668614120" ref="B46:L49" totalsRowShown="0" headerRowDxfId="169" dataDxfId="167" headerRowBorderDxfId="168" tableBorderDxfId="166" totalsRowBorderDxfId="165">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="119" xr:uid="{7AB81B42-CAF1-425D-A49A-BB0B3891506C}" name="Tabla1927668614120" displayName="Tabla1927668614120" ref="B46:L49" totalsRowShown="0" headerRowDxfId="165" dataDxfId="163" headerRowBorderDxfId="164" tableBorderDxfId="162" totalsRowBorderDxfId="161">
   <autoFilter ref="B46:L49" xr:uid="{7AB81B42-CAF1-425D-A49A-BB0B3891506C}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{B3C3C5C4-9163-4BB8-8CB2-2CA9A49F86D6}" name="ID Noticias" dataDxfId="164"/>
-    <tableColumn id="2" xr3:uid="{658EB93B-8FFC-4222-B2BF-0CE1A5868BDB}" name="Titulo" dataDxfId="163"/>
-    <tableColumn id="3" xr3:uid="{C37291EB-8099-4591-8BC0-E54DCCE798DF}" name="Encabezado" dataDxfId="162"/>
-    <tableColumn id="4" xr3:uid="{19DF6349-ACEA-40B6-9494-F3B3A55F14D8}" name="DescripcionPrincipal" dataDxfId="161"/>
-    <tableColumn id="5" xr3:uid="{F8950E52-F394-463F-BCF9-F6A09093101C}" name="Descripcion2 (opcional)" dataDxfId="160"/>
-    <tableColumn id="6" xr3:uid="{86E8CA4B-CE0C-4DCE-AEA2-8A36C69B9828}" name="Descripcion3 (opcional)" dataDxfId="159"/>
-    <tableColumn id="7" xr3:uid="{E5343DF4-D159-4DA3-9100-C024D63EE82B}" name="ImagenEncabezado" dataDxfId="158"/>
-    <tableColumn id="8" xr3:uid="{802BA2EA-EF6F-4CED-961F-E0306283A1F4}" name="ImagenPrincipal" dataDxfId="157"/>
-    <tableColumn id="9" xr3:uid="{D1EE4BCF-8B4D-4686-BF2D-2DFB2D31C054}" name="ImagenSecundaria" dataDxfId="156"/>
-    <tableColumn id="10" xr3:uid="{F83EC609-A166-475E-862C-679A059E0502}" name="Fecha" dataDxfId="155"/>
-    <tableColumn id="11" xr3:uid="{8C6786D1-B326-4209-A55C-D802C4E13663}" name="ID Tipo" dataDxfId="154"/>
+    <tableColumn id="1" xr3:uid="{B3C3C5C4-9163-4BB8-8CB2-2CA9A49F86D6}" name="ID Noticias" dataDxfId="160"/>
+    <tableColumn id="2" xr3:uid="{658EB93B-8FFC-4222-B2BF-0CE1A5868BDB}" name="Titulo" dataDxfId="159"/>
+    <tableColumn id="3" xr3:uid="{C37291EB-8099-4591-8BC0-E54DCCE798DF}" name="Encabezado" dataDxfId="158"/>
+    <tableColumn id="4" xr3:uid="{19DF6349-ACEA-40B6-9494-F3B3A55F14D8}" name="DescripcionPrincipal" dataDxfId="157"/>
+    <tableColumn id="5" xr3:uid="{F8950E52-F394-463F-BCF9-F6A09093101C}" name="Descripcion2 (opcional)" dataDxfId="156"/>
+    <tableColumn id="6" xr3:uid="{86E8CA4B-CE0C-4DCE-AEA2-8A36C69B9828}" name="Descripcion3 (opcional)" dataDxfId="155"/>
+    <tableColumn id="7" xr3:uid="{E5343DF4-D159-4DA3-9100-C024D63EE82B}" name="ImagenEncabezado" dataDxfId="154"/>
+    <tableColumn id="8" xr3:uid="{802BA2EA-EF6F-4CED-961F-E0306283A1F4}" name="ImagenPrincipal" dataDxfId="153"/>
+    <tableColumn id="9" xr3:uid="{D1EE4BCF-8B4D-4686-BF2D-2DFB2D31C054}" name="ImagenSecundaria" dataDxfId="152"/>
+    <tableColumn id="10" xr3:uid="{F83EC609-A166-475E-862C-679A059E0502}" name="Fecha" dataDxfId="151"/>
+    <tableColumn id="11" xr3:uid="{8C6786D1-B326-4209-A55C-D802C4E13663}" name="ID Tipo" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="120" xr:uid="{0F5369E4-CE2B-45F9-AF61-1EA42572570D}" name="Tabla134121" displayName="Tabla134121" ref="N46:O49" totalsRowShown="0" headerRowDxfId="153" dataDxfId="151" headerRowBorderDxfId="152" tableBorderDxfId="150" totalsRowBorderDxfId="149">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="120" xr:uid="{0F5369E4-CE2B-45F9-AF61-1EA42572570D}" name="Tabla134121" displayName="Tabla134121" ref="N46:O49" totalsRowShown="0" headerRowDxfId="149" dataDxfId="147" headerRowBorderDxfId="148" tableBorderDxfId="146" totalsRowBorderDxfId="145">
   <autoFilter ref="N46:O49" xr:uid="{0F5369E4-CE2B-45F9-AF61-1EA42572570D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E92E76AB-4D6C-452B-A24C-6A46A4B79732}" name="ID Tipo" dataDxfId="148"/>
-    <tableColumn id="2" xr3:uid="{1CE79D9C-B994-4903-8F01-8218F4D10587}" name="Tipos" dataDxfId="147"/>
+    <tableColumn id="1" xr3:uid="{E92E76AB-4D6C-452B-A24C-6A46A4B79732}" name="ID Tipo" dataDxfId="144"/>
+    <tableColumn id="2" xr3:uid="{1CE79D9C-B994-4903-8F01-8218F4D10587}" name="Tipos" dataDxfId="143"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="121" xr:uid="{60D4DD1A-0BFD-4BDC-86DA-762A7224B420}" name="Tabla511101122" displayName="Tabla511101122" ref="B4:O7" totalsRowShown="0" headerRowDxfId="146" dataDxfId="144" headerRowBorderDxfId="145" tableBorderDxfId="143" totalsRowBorderDxfId="142">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="121" xr:uid="{60D4DD1A-0BFD-4BDC-86DA-762A7224B420}" name="Tabla511101122" displayName="Tabla511101122" ref="B4:O7" totalsRowShown="0" headerRowDxfId="142" dataDxfId="140" headerRowBorderDxfId="141" tableBorderDxfId="139" totalsRowBorderDxfId="138">
   <autoFilter ref="B4:O7" xr:uid="{5060941E-1162-428A-A2E9-444AAF70D817}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{6906DFE3-F50E-4AB7-9344-B63F4B29069F}" name="N.O Documento" dataDxfId="141"/>
-    <tableColumn id="2" xr3:uid="{6A7863AF-F0F0-4F8A-AAE4-8E1CF172B2AD}" name="ID Tipo Documento" dataDxfId="140"/>
-    <tableColumn id="3" xr3:uid="{FD3D3C9C-C29F-4F8D-9D71-2C8ACA973812}" name="Contraseña" dataDxfId="139" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="16" xr3:uid="{84A95125-1F37-4DBB-ADD2-F205C02C5BB6}" name="Primer Nombre" dataDxfId="138" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="17" xr3:uid="{CA716993-A589-4FFA-BA06-0349ACA45479}" name="Segundo Nombre" dataDxfId="137"/>
-    <tableColumn id="4" xr3:uid="{81DB0449-6DF4-4F1E-BB4C-B10527988F16}" name="Primer Apellido" dataDxfId="136"/>
-    <tableColumn id="18" xr3:uid="{D3DFE98E-5C42-4A6B-BFF1-92D5F8550277}" name="Segundo Apellido" dataDxfId="135"/>
-    <tableColumn id="5" xr3:uid="{15522115-48A1-4E4C-BCD5-E8279E508162}" name="Correo1" dataDxfId="134" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="6" xr3:uid="{AF449940-BC90-49BA-BAD5-69244CC7DABD}" name="Correo2" dataDxfId="133" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="7" xr3:uid="{DF49063F-2C5C-401E-9957-829A47959EDD}" name="Contacto1" dataDxfId="132"/>
-    <tableColumn id="19" xr3:uid="{82BFE35C-5A98-44E5-8E06-018E659096BD}" name="Contacto2" dataDxfId="131"/>
-    <tableColumn id="10" xr3:uid="{C3E5B87E-7F3B-4C25-BD83-D79E66983D17}" name="Fecha Nacimiento" dataDxfId="130"/>
-    <tableColumn id="11" xr3:uid="{7B6F9A52-CB4A-4522-958A-9B9D8B6C3B13}" name="Foto" dataDxfId="129"/>
-    <tableColumn id="12" xr3:uid="{A0BEAFF5-90D2-45C3-8EF4-F32292150250}" name="ID Rol" dataDxfId="128"/>
+    <tableColumn id="1" xr3:uid="{6906DFE3-F50E-4AB7-9344-B63F4B29069F}" name="N.O Documento" dataDxfId="137"/>
+    <tableColumn id="2" xr3:uid="{6A7863AF-F0F0-4F8A-AAE4-8E1CF172B2AD}" name="ID Tipo Documento" dataDxfId="136"/>
+    <tableColumn id="3" xr3:uid="{FD3D3C9C-C29F-4F8D-9D71-2C8ACA973812}" name="Contraseña" dataDxfId="135" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="16" xr3:uid="{84A95125-1F37-4DBB-ADD2-F205C02C5BB6}" name="Primer Nombre" dataDxfId="134" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="17" xr3:uid="{CA716993-A589-4FFA-BA06-0349ACA45479}" name="Segundo Nombre" dataDxfId="133"/>
+    <tableColumn id="4" xr3:uid="{81DB0449-6DF4-4F1E-BB4C-B10527988F16}" name="Primer Apellido" dataDxfId="132"/>
+    <tableColumn id="18" xr3:uid="{D3DFE98E-5C42-4A6B-BFF1-92D5F8550277}" name="Segundo Apellido" dataDxfId="131"/>
+    <tableColumn id="5" xr3:uid="{15522115-48A1-4E4C-BCD5-E8279E508162}" name="Correo1" dataDxfId="130" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="6" xr3:uid="{AF449940-BC90-49BA-BAD5-69244CC7DABD}" name="Correo2" dataDxfId="129" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="7" xr3:uid="{DF49063F-2C5C-401E-9957-829A47959EDD}" name="Contacto1" dataDxfId="128"/>
+    <tableColumn id="19" xr3:uid="{82BFE35C-5A98-44E5-8E06-018E659096BD}" name="Contacto2" dataDxfId="127"/>
+    <tableColumn id="10" xr3:uid="{C3E5B87E-7F3B-4C25-BD83-D79E66983D17}" name="Fecha Nacimiento" dataDxfId="126"/>
+    <tableColumn id="11" xr3:uid="{7B6F9A52-CB4A-4522-958A-9B9D8B6C3B13}" name="Foto" dataDxfId="125"/>
+    <tableColumn id="12" xr3:uid="{A0BEAFF5-90D2-45C3-8EF4-F32292150250}" name="ID Rol" dataDxfId="124"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="122" xr:uid="{6E8CB120-6F11-4C0C-96DD-CB57015C7322}" name="Tabla2739424471102123" displayName="Tabla2739424471102123" ref="B11:C14" totalsRowShown="0" headerRowDxfId="127" dataDxfId="125" headerRowBorderDxfId="126" tableBorderDxfId="124" totalsRowBorderDxfId="123">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="122" xr:uid="{6E8CB120-6F11-4C0C-96DD-CB57015C7322}" name="Tabla2739424471102123" displayName="Tabla2739424471102123" ref="B11:C14" totalsRowShown="0" headerRowDxfId="123" dataDxfId="121" headerRowBorderDxfId="122" tableBorderDxfId="120" totalsRowBorderDxfId="119">
   <autoFilter ref="B11:C14" xr:uid="{96F826A9-125A-402B-8294-7BD6C4B2585A}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3E58DF26-B2BB-4811-8A0B-3A4C4D521A5D}" name="ID Tipo Documento" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{F6784414-4DDC-4249-8FC7-B7EF2AF8BA43}" name="Tipo Documento" dataDxfId="121"/>
+    <tableColumn id="1" xr3:uid="{3E58DF26-B2BB-4811-8A0B-3A4C4D521A5D}" name="ID Tipo Documento" dataDxfId="118"/>
+    <tableColumn id="2" xr3:uid="{F6784414-4DDC-4249-8FC7-B7EF2AF8BA43}" name="Tipo Documento" dataDxfId="117"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="123" xr:uid="{67492D1B-A5B8-4C7F-A10E-F9CF8B7AC734}" name="Tabla294169107124" displayName="Tabla294169107124" ref="E11:H14" totalsRowShown="0" headerRowDxfId="120" dataDxfId="118" headerRowBorderDxfId="119" tableBorderDxfId="117" totalsRowBorderDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="123" xr:uid="{67492D1B-A5B8-4C7F-A10E-F9CF8B7AC734}" name="Tabla294169107124" displayName="Tabla294169107124" ref="E11:H14" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115" tableBorderDxfId="113" totalsRowBorderDxfId="112">
   <autoFilter ref="E11:H14" xr:uid="{6AFC29F1-F786-4DAE-882B-704F8ED9CCDC}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{82C10963-94CA-40E8-A1CE-F62235830D2C}" name="ID Curso" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{9301AED3-7CE9-4660-8632-00CA00EA06B8}" name="Nombre Curso" dataDxfId="114"/>
-    <tableColumn id="4" xr3:uid="{84C6634B-85BD-4582-A811-A5EEA06DE73B}" name="ID Jornada" dataDxfId="113"/>
-    <tableColumn id="5" xr3:uid="{83F8BAFB-C9E1-426B-991B-502B422F6F37}" name="ID Grado" dataDxfId="112"/>
+    <tableColumn id="1" xr3:uid="{82C10963-94CA-40E8-A1CE-F62235830D2C}" name="ID Curso" dataDxfId="111"/>
+    <tableColumn id="2" xr3:uid="{9301AED3-7CE9-4660-8632-00CA00EA06B8}" name="Nombre Curso" dataDxfId="110"/>
+    <tableColumn id="4" xr3:uid="{84C6634B-85BD-4582-A811-A5EEA06DE73B}" name="ID Jornada" dataDxfId="109"/>
+    <tableColumn id="5" xr3:uid="{83F8BAFB-C9E1-426B-991B-502B422F6F37}" name="ID Grado" dataDxfId="108"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="124" xr:uid="{F59C0BDE-0549-481B-BA78-351E8A95B778}" name="Tabla304645507791108125" displayName="Tabla304645507791108125" ref="J11:L14" totalsRowShown="0" headerRowDxfId="111" dataDxfId="109" headerRowBorderDxfId="110" tableBorderDxfId="108" totalsRowBorderDxfId="107">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="124" xr:uid="{F59C0BDE-0549-481B-BA78-351E8A95B778}" name="Tabla304645507791108125" displayName="Tabla304645507791108125" ref="J11:L14" totalsRowShown="0" headerRowDxfId="107" dataDxfId="105" headerRowBorderDxfId="106" tableBorderDxfId="104" totalsRowBorderDxfId="103">
   <autoFilter ref="J11:L14" xr:uid="{FA5780ED-E3E2-4440-B85D-AF7EE1910729}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{ECC0E832-BB14-4085-9424-7F42619F55E6}" name="ID Grado" dataDxfId="106"/>
-    <tableColumn id="2" xr3:uid="{EEA69F5D-1FE6-49B1-ABEE-BB3A6E32639C}" name="Grado" dataDxfId="105"/>
-    <tableColumn id="3" xr3:uid="{F314B58B-6C99-4D9E-BDBA-4E47DA362E97}" name="Descripcion" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{ECC0E832-BB14-4085-9424-7F42619F55E6}" name="ID Grado" dataDxfId="102"/>
+    <tableColumn id="2" xr3:uid="{EEA69F5D-1FE6-49B1-ABEE-BB3A6E32639C}" name="Grado" dataDxfId="101"/>
+    <tableColumn id="3" xr3:uid="{F314B58B-6C99-4D9E-BDBA-4E47DA362E97}" name="Descripcion" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="125" xr:uid="{74D2AAED-AE03-4E02-85B9-17C92392F983}" name="Tabla284749537893109126" displayName="Tabla284749537893109126" ref="N11:P14" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103" tableBorderDxfId="101" totalsRowBorderDxfId="100">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="125" xr:uid="{74D2AAED-AE03-4E02-85B9-17C92392F983}" name="Tabla284749537893109126" displayName="Tabla284749537893109126" ref="N11:P14" totalsRowShown="0" headerRowDxfId="99" dataDxfId="97" headerRowBorderDxfId="98" tableBorderDxfId="96" totalsRowBorderDxfId="95">
   <autoFilter ref="N11:P14" xr:uid="{DA57B9DC-92DD-4AC7-A195-38CD05C19C53}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0E4CBB59-94B8-4FB4-8D03-E8B8A21A7626}" name="ID Jornada" dataDxfId="99"/>
-    <tableColumn id="2" xr3:uid="{BD574BA4-5183-42F7-93E0-42E49E3FC6F1}" name="Jornada" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{EECC3728-50C0-4D77-AA9C-45279D89ECD3}" name="Descripcion" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{0E4CBB59-94B8-4FB4-8D03-E8B8A21A7626}" name="ID Jornada" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{BD574BA4-5183-42F7-93E0-42E49E3FC6F1}" name="Jornada" dataDxfId="93"/>
+    <tableColumn id="3" xr3:uid="{EECC3728-50C0-4D77-AA9C-45279D89ECD3}" name="Descripcion" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="126" xr:uid="{5E4CDA82-0587-4AE3-98E5-85525C4A1006}" name="Tabla3440437094110127" displayName="Tabla3440437094110127" ref="R11:S15" totalsRowShown="0" headerRowDxfId="97" dataDxfId="95" headerRowBorderDxfId="96" tableBorderDxfId="94" totalsRowBorderDxfId="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="126" xr:uid="{5E4CDA82-0587-4AE3-98E5-85525C4A1006}" name="Tabla3440437094110127" displayName="Tabla3440437094110127" ref="R11:S15" totalsRowShown="0" headerRowDxfId="91" dataDxfId="89" headerRowBorderDxfId="90" tableBorderDxfId="88" totalsRowBorderDxfId="87">
   <autoFilter ref="R11:S15" xr:uid="{6F50273C-5B06-49A3-A04D-115455B03FC0}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0A8FEFD0-D4BE-4363-86B0-57F1F5FB3A07}" name="ID Rol" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{D7A118F0-AC10-41B3-AF30-E635D00CEEB1}" name="Rol" dataDxfId="91"/>
+    <tableColumn id="1" xr3:uid="{0A8FEFD0-D4BE-4363-86B0-57F1F5FB3A07}" name="ID Rol" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{D7A118F0-AC10-41B3-AF30-E635D00CEEB1}" name="Rol" dataDxfId="85"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table39.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="127" xr:uid="{2E199736-F4D0-4CBE-93C0-9AA6B77DAABE}" name="Tabla445675112128" displayName="Tabla445675112128" ref="Q4:R7" totalsRowShown="0" headerRowDxfId="90" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87" totalsRowBorderDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="127" xr:uid="{2E199736-F4D0-4CBE-93C0-9AA6B77DAABE}" name="Tabla445675112128" displayName="Tabla445675112128" ref="Q4:R7" totalsRowShown="0" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81" totalsRowBorderDxfId="80">
   <autoFilter ref="Q4:R7" xr:uid="{BE369BB5-2313-49C1-AE4E-721B3E8B5017}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BF6F496C-969D-4077-97D4-921D3E1AE64A}" name="ID Curso" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{90C41B13-5A0E-49BA-8E1D-EBD12F8D1661}" name="ID Usuarios" dataDxfId="84"/>
+    <tableColumn id="1" xr3:uid="{BF6F496C-969D-4077-97D4-921D3E1AE64A}" name="ID Curso" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{90C41B13-5A0E-49BA-8E1D-EBD12F8D1661}" name="ID Usuarios" dataDxfId="78"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1114AA21-2CF5-4C13-B74F-FEB2F5D10CAD}" name="Tabla9" displayName="Tabla9" ref="B25:G28" totalsRowShown="0" headerRowDxfId="414" dataDxfId="412" headerRowBorderDxfId="413" tableBorderDxfId="411" totalsRowBorderDxfId="410">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1114AA21-2CF5-4C13-B74F-FEB2F5D10CAD}" name="Tabla9" displayName="Tabla9" ref="B25:G28" totalsRowShown="0" headerRowDxfId="410" dataDxfId="408" headerRowBorderDxfId="409" tableBorderDxfId="407" totalsRowBorderDxfId="406">
   <autoFilter ref="B25:G28" xr:uid="{1114AA21-2CF5-4C13-B74F-FEB2F5D10CAD}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C50BDD45-68D8-4796-8F7C-5629680739A8}" name="Titulo" dataDxfId="409"/>
-    <tableColumn id="2" xr3:uid="{C23939D4-3063-4D02-B6D7-50952A0CA7F2}" name="Encabezado" dataDxfId="408"/>
-    <tableColumn id="3" xr3:uid="{BC6DDE66-7E27-447D-8E83-5B934A8AED11}" name="Descripcion1" dataDxfId="407"/>
-    <tableColumn id="4" xr3:uid="{B260C3F2-7D1E-425E-BB32-50E51690891D}" name="Imagen 1" dataDxfId="406"/>
-    <tableColumn id="5" xr3:uid="{9D1D15E8-1446-4FFC-A6CF-DEF0D012D46F}" name="Fecha" dataDxfId="405"/>
-    <tableColumn id="6" xr3:uid="{7BE9F49A-7697-4E6E-A40A-7A0112BA8909}" name="Tipos" dataDxfId="404"/>
+    <tableColumn id="1" xr3:uid="{C50BDD45-68D8-4796-8F7C-5629680739A8}" name="Titulo" dataDxfId="405"/>
+    <tableColumn id="2" xr3:uid="{C23939D4-3063-4D02-B6D7-50952A0CA7F2}" name="Encabezado" dataDxfId="404"/>
+    <tableColumn id="3" xr3:uid="{BC6DDE66-7E27-447D-8E83-5B934A8AED11}" name="Descripcion1" dataDxfId="403"/>
+    <tableColumn id="4" xr3:uid="{B260C3F2-7D1E-425E-BB32-50E51690891D}" name="Imagen 1" dataDxfId="402"/>
+    <tableColumn id="5" xr3:uid="{9D1D15E8-1446-4FFC-A6CF-DEF0D012D46F}" name="Fecha" dataDxfId="401"/>
+    <tableColumn id="6" xr3:uid="{7BE9F49A-7697-4E6E-A40A-7A0112BA8909}" name="Tipos" dataDxfId="400"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table40.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="128" xr:uid="{9AEDA9F9-29D1-4DC9-8B85-DD1ABFE354CB}" name="Tabla813113129" displayName="Tabla813113129" ref="B18:G21" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="128" xr:uid="{9AEDA9F9-29D1-4DC9-8B85-DD1ABFE354CB}" name="Tabla813113129" displayName="Tabla813113129" ref="B18:G21" totalsRowShown="0" headerRowDxfId="77" dataDxfId="76">
   <autoFilter ref="B18:G21" xr:uid="{55D91AD9-4F03-4F28-B743-376E8454B15C}"/>
   <tableColumns count="6">
-    <tableColumn id="6" xr3:uid="{9DFF507E-904B-4084-97D1-4131F740C172}" name="ID Horario" dataDxfId="81"/>
-    <tableColumn id="1" xr3:uid="{2E310A6F-3F86-45A4-9EB2-322C222415BA}" name="Titulo Horario" dataDxfId="80"/>
-    <tableColumn id="2" xr3:uid="{07DC9571-D039-4CDC-AF54-A62B4100D92D}" name="Imagen Horario" dataDxfId="79"/>
-    <tableColumn id="3" xr3:uid="{761F6FD9-8EE2-4EFA-924C-F6CB77A2BFE7}" name="Descripcion" dataDxfId="78"/>
-    <tableColumn id="4" xr3:uid="{827CAF12-0E49-4245-927A-9018C1481A7B}" name="Curso" dataDxfId="77"/>
-    <tableColumn id="5" xr3:uid="{C03162FE-2155-4DA0-B0DE-AF2D9D1C16B1}" name="ID Profesor" dataDxfId="76"/>
+    <tableColumn id="6" xr3:uid="{9DFF507E-904B-4084-97D1-4131F740C172}" name="ID Horario" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{2E310A6F-3F86-45A4-9EB2-322C222415BA}" name="Titulo Horario" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{07DC9571-D039-4CDC-AF54-A62B4100D92D}" name="Imagen Horario" dataDxfId="73"/>
+    <tableColumn id="3" xr3:uid="{761F6FD9-8EE2-4EFA-924C-F6CB77A2BFE7}" name="Descripcion" dataDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{827CAF12-0E49-4245-927A-9018C1481A7B}" name="Curso" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{C03162FE-2155-4DA0-B0DE-AF2D9D1C16B1}" name="ID Profesor" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table41.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="129" xr:uid="{A804767C-77CB-454B-8EDA-3BBFB86D8C0D}" name="Tabla712114130" displayName="Tabla712114130" ref="B25:F28" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="129" xr:uid="{A804767C-77CB-454B-8EDA-3BBFB86D8C0D}" name="Tabla712114130" displayName="Tabla712114130" ref="B25:F28" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="B25:F28" xr:uid="{0391CE60-4033-4537-BDDF-CE0B8EAF1519}"/>
   <tableColumns count="5">
-    <tableColumn id="26" xr3:uid="{426672B9-13AE-4944-B115-24C9B8128E0D}" name="ID Aula" dataDxfId="73"/>
-    <tableColumn id="1" xr3:uid="{0D178C11-DF46-4F84-84DB-AEBA972942B5}" name="Nombre Aula" dataDxfId="72"/>
-    <tableColumn id="2" xr3:uid="{182D18F2-E95B-4ED8-BCFE-569455E8218E}" name="ID Materia" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{B955ADE3-6DA9-4A81-A7F5-1E9E2F9158F8}" name="Profesor" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{94E3707E-B873-429D-A0BC-9D4E6D962287}" name="Curso" dataDxfId="70"/>
+    <tableColumn id="26" xr3:uid="{426672B9-13AE-4944-B115-24C9B8128E0D}" name="ID Aula" dataDxfId="67"/>
+    <tableColumn id="1" xr3:uid="{0D178C11-DF46-4F84-84DB-AEBA972942B5}" name="Nombre Aula" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{182D18F2-E95B-4ED8-BCFE-569455E8218E}" name="ID Materia" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{B955ADE3-6DA9-4A81-A7F5-1E9E2F9158F8}" name="Profesor" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{94E3707E-B873-429D-A0BC-9D4E6D962287}" name="Curso" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table42.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="130" xr:uid="{792E564F-96E9-4074-B486-B627E74D7C59}" name="Tabla356576115131" displayName="Tabla356576115131" ref="I18:K21" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66" totalsRowBorderDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="130" xr:uid="{792E564F-96E9-4074-B486-B627E74D7C59}" name="Tabla356576115131" displayName="Tabla356576115131" ref="I18:K21" totalsRowShown="0" headerRowDxfId="62" dataDxfId="60" headerRowBorderDxfId="61" tableBorderDxfId="59" totalsRowBorderDxfId="58">
   <autoFilter ref="I18:K21" xr:uid="{5E1CA139-BBA4-4E67-B3D6-4EDA817A9C11}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1FFFB345-5DAA-4B53-816E-C1B2801481AF}" name="ID Materia" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{545B12D6-FBA8-40BB-A552-3D24067465C3}" name="Nombre Materia" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{4A6A3CC6-6851-49BA-84AF-8AD504A1EBC4}" name="Descripcion" dataDxfId="62"/>
+    <tableColumn id="1" xr3:uid="{1FFFB345-5DAA-4B53-816E-C1B2801481AF}" name="ID Materia" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{545B12D6-FBA8-40BB-A552-3D24067465C3}" name="Nombre Materia" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{4A6A3CC6-6851-49BA-84AF-8AD504A1EBC4}" name="Descripcion" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14340,177 +14211,175 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="131" xr:uid="{98995379-0C61-4428-A5BD-76EA1528B9F5}" name="Tabla94116132" displayName="Tabla94116132" ref="H25:N28" totalsRowShown="0">
   <autoFilter ref="H25:N28" xr:uid="{FD592122-3947-4ECC-BC98-E6BEC5688EDD}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{491BC544-6C7D-4702-AFE7-2A76E79A8F0C}" name="ID Anuncios" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{FD5EE7AF-9725-416F-8D82-B5117B773137}" name="Titulo" dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{6D581094-0976-4027-AF53-8E08E4F774AF}" name="Descripcion Anuncios" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{2B7FFD39-8151-4770-BE6B-97E23F63A65B}" name="Archivo" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{EFD574DA-E1C5-426E-822B-2DE6EB8B1F31}" name="Fecha" dataDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{9500BBBC-56F1-474B-B910-A8C14ACB603F}" name="ID Aula" dataDxfId="56"/>
-    <tableColumn id="8" xr3:uid="{B235130F-54AB-4C41-9F3E-C74F387A8AED}" name="ID Usuario" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{491BC544-6C7D-4702-AFE7-2A76E79A8F0C}" name="ID Anuncios" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{FD5EE7AF-9725-416F-8D82-B5117B773137}" name="Titulo" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{6D581094-0976-4027-AF53-8E08E4F774AF}" name="Descripcion Anuncios" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{2B7FFD39-8151-4770-BE6B-97E23F63A65B}" name="Archivo" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{EFD574DA-E1C5-426E-822B-2DE6EB8B1F31}" name="Fecha" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{9500BBBC-56F1-474B-B910-A8C14ACB603F}" name="ID Aula" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{B235130F-54AB-4C41-9F3E-C74F387A8AED}" name="ID Usuario" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table44.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="132" xr:uid="{FDBB96F5-0232-4F5E-83B3-798403E683AE}" name="Tabla95117133" displayName="Tabla95117133" ref="B32:G35" totalsRowShown="0">
-  <autoFilter ref="B32:G35" xr:uid="{880FB7CA-779A-498E-8F82-CEF190178801}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8B3D0AE6-6376-4447-A3B2-2F77FA2C277C}" name="ID Trabajos" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{B0297F4C-D0C5-4D18-AFB6-2DBED0DF9F7C}" name="Titulo Trabajo" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{DEA33B23-CAFA-4FBB-9644-EE0CD18C23BA}" name="Descripcion Trabajos" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{FEB979E7-0D52-457C-B674-671E6A945F10}" name="Archivo" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{A2B43797-4AD2-451A-A2CD-ED4228275E0C}" name="Fecha Entrega" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{DB305FE6-FA03-4037-9080-BA61A3CAA310}" name="ID Aula" dataDxfId="49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="132" xr:uid="{FDBB96F5-0232-4F5E-83B3-798403E683AE}" name="Tabla95117133" displayName="Tabla95117133" ref="B32:F35" totalsRowShown="0">
+  <autoFilter ref="B32:F35" xr:uid="{880FB7CA-779A-498E-8F82-CEF190178801}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{8B3D0AE6-6376-4447-A3B2-2F77FA2C277C}" name="ID Trabajos" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{B0297F4C-D0C5-4D18-AFB6-2DBED0DF9F7C}" name="Titulo Trabajo" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{DEA33B23-CAFA-4FBB-9644-EE0CD18C23BA}" name="Descripcion Trabajos" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{A2B43797-4AD2-451A-A2CD-ED4228275E0C}" name="Fecha Entrega" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{DB305FE6-FA03-4037-9080-BA61A3CAA310}" name="ID Aula" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table45.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="133" xr:uid="{31888CF0-C84E-4DA7-A842-C7DE61CC0F79}" name="Tabla498118134" displayName="Tabla498118134" ref="I32:N35" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
-  <autoFilter ref="I32:N35" xr:uid="{6332F8B1-622B-404B-AAB5-81232D7A9F73}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="133" xr:uid="{31888CF0-C84E-4DA7-A842-C7DE61CC0F79}" name="Tabla498118134" displayName="Tabla498118134" ref="H32:M35" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+  <autoFilter ref="H32:M35" xr:uid="{6332F8B1-622B-404B-AAB5-81232D7A9F73}"/>
   <tableColumns count="6">
-    <tableColumn id="3" xr3:uid="{B270D11F-CCB8-4070-8307-577866C6CF87}" name="ID comentario" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{A100A0CA-89CB-46A7-811D-A9F795E11E8C}" name="Descripcion" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{B5C79879-8AE8-4EE5-AC73-B5E0E0120007}" name="Fecha" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{B88B0163-7B22-4D47-B31B-0B1F5F9CE6E7}" name="ID Usuario" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{CE1FAE57-F908-498E-B089-DB4924729A42}" name="ID Anuncios" dataDxfId="39"/>
-    <tableColumn id="1" xr3:uid="{BCD7E615-A02D-48E5-8D9C-4B39866754A3}" name="ID Trabajos" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{B270D11F-CCB8-4070-8307-577866C6CF87}" name="ID comentario" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{A100A0CA-89CB-46A7-811D-A9F795E11E8C}" name="Descripcion" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{B5C79879-8AE8-4EE5-AC73-B5E0E0120007}" name="Fecha" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{B88B0163-7B22-4D47-B31B-0B1F5F9CE6E7}" name="ID Usuario" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{CE1FAE57-F908-498E-B089-DB4924729A42}" name="ID Anuncios" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{BCD7E615-A02D-48E5-8D9C-4B39866754A3}" name="ID Trabajos" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table46.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="134" xr:uid="{F0B3EB2A-C5BE-4B0B-9AA7-3E6171A7354F}" name="Tabla699119135" displayName="Tabla699119135" ref="B39:G42" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34">
-  <autoFilter ref="B39:G42" xr:uid="{4382CBAB-F3D6-47DB-B226-67050DE66316}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D59F3BD0-2EFE-4C38-A8AC-62B2BFF48224}" name="ID entregados" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{90A0DD42-7017-4212-B4C8-686716AE281D}" name="Archivo" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{56A400A0-840D-4171-8D0F-39B17E7B8DDC}" name="Fecha Entrega" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{DF58D687-96AC-4DDA-AD8C-77BBB87489CC}" name="Nota" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{E6FB96C4-974F-4C5F-9040-365B8F11303A}" name="ID Usuario" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{5A5EF9CB-515B-4F41-BC0B-5F8CCDE0DF2C}" name="ID Trabajos" dataDxfId="28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="134" xr:uid="{F0B3EB2A-C5BE-4B0B-9AA7-3E6171A7354F}" name="Tabla699119135" displayName="Tabla699119135" ref="B39:F42" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28">
+  <autoFilter ref="B39:F42" xr:uid="{4382CBAB-F3D6-47DB-B226-67050DE66316}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D59F3BD0-2EFE-4C38-A8AC-62B2BFF48224}" name="ID entregados" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{56A400A0-840D-4171-8D0F-39B17E7B8DDC}" name="Fecha Entrega" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{DF58D687-96AC-4DDA-AD8C-77BBB87489CC}" name="Nota" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{E6FB96C4-974F-4C5F-9040-365B8F11303A}" name="ID Usuario" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{5A5EF9CB-515B-4F41-BC0B-5F8CCDE0DF2C}" name="ID Trabajos" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table47.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="135" xr:uid="{D2D9DB2D-B32D-4330-94F2-D5F7DE1CFB5B}" name="Tabla1927668614120136" displayName="Tabla1927668614120136" ref="B46:L49" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="135" xr:uid="{D2D9DB2D-B32D-4330-94F2-D5F7DE1CFB5B}" name="Tabla1927668614120136" displayName="Tabla1927668614120136" ref="B46:L49" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="B46:L49" xr:uid="{7AB81B42-CAF1-425D-A49A-BB0B3891506C}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{95E09BBE-5C30-4D1D-B212-D316E157B537}" name="ID Noticias" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{F753836B-FAA0-4F1B-9D80-F6D0CC92CED3}" name="Titulo" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{15C4E881-E045-49A7-811D-44EDE7C8732C}" name="Encabezado" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{4D18E346-99B1-40DA-AE09-0BEDC8E78E39}" name="DescripcionPrincipal" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{92E08230-4418-4E5D-B4D1-0AA86CFD66A4}" name="Descripcion2 (opcional)" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{B9B21C74-1235-482D-9271-05974F582306}" name="Descripcion3 (opcional)" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{054F1938-836C-4AF9-8F74-E9DFFE9ECD53}" name="ImagenEncabezado" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{A76004CA-EF24-4778-A60C-CC7FA0DF4548}" name="ImagenPrincipal" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{F8DEACE6-E1A5-4445-9683-105FDB02400B}" name="ImagenSecundaria" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{B40115F8-695E-4F12-B5B7-ECF2376E6B51}" name="Fecha" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{FBF8A556-052A-4E9F-8802-8122D1F8CCF2}" name="ID Tipo" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{95E09BBE-5C30-4D1D-B212-D316E157B537}" name="ID Noticias" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{F753836B-FAA0-4F1B-9D80-F6D0CC92CED3}" name="Titulo" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{15C4E881-E045-49A7-811D-44EDE7C8732C}" name="Encabezado" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{4D18E346-99B1-40DA-AE09-0BEDC8E78E39}" name="DescripcionPrincipal" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{92E08230-4418-4E5D-B4D1-0AA86CFD66A4}" name="Descripcion2 (opcional)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{B9B21C74-1235-482D-9271-05974F582306}" name="Descripcion3 (opcional)" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{054F1938-836C-4AF9-8F74-E9DFFE9ECD53}" name="ImagenEncabezado" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{A76004CA-EF24-4778-A60C-CC7FA0DF4548}" name="ImagenPrincipal" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{F8DEACE6-E1A5-4445-9683-105FDB02400B}" name="ImagenSecundaria" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{B40115F8-695E-4F12-B5B7-ECF2376E6B51}" name="Fecha" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{FBF8A556-052A-4E9F-8802-8122D1F8CCF2}" name="ID Tipo" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table48.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="136" xr:uid="{788EF3AA-BEB6-4BB9-B6A2-BC00A16D1A7F}" name="Tabla134121137" displayName="Tabla134121137" ref="N46:O49" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="136" xr:uid="{788EF3AA-BEB6-4BB9-B6A2-BC00A16D1A7F}" name="Tabla134121137" displayName="Tabla134121137" ref="N46:O49" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="N46:O49" xr:uid="{0F5369E4-CE2B-45F9-AF61-1EA42572570D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{329AACB7-D05F-4C3A-9CC1-3B53C9666536}" name="ID Tipo" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{107ED8A2-471A-47E2-8F30-D68252B03310}" name="Tipos" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{329AACB7-D05F-4C3A-9CC1-3B53C9666536}" name="ID Tipo" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{107ED8A2-471A-47E2-8F30-D68252B03310}" name="Tipos" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{186BC145-C9BD-40A3-A5EC-987E219A2D70}" name="Tabla511" displayName="Tabla511" ref="B3:R6" totalsRowShown="0" headerRowDxfId="403" dataDxfId="401" headerRowBorderDxfId="402" tableBorderDxfId="400" totalsRowBorderDxfId="399">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{186BC145-C9BD-40A3-A5EC-987E219A2D70}" name="Tabla511" displayName="Tabla511" ref="B3:R6" totalsRowShown="0" headerRowDxfId="399" dataDxfId="397" headerRowBorderDxfId="398" tableBorderDxfId="396" totalsRowBorderDxfId="395">
   <autoFilter ref="B3:R6" xr:uid="{186BC145-C9BD-40A3-A5EC-987E219A2D70}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{7318D55B-472C-40E5-B77D-F547B319090B}" name="N.O Documento" dataDxfId="398"/>
-    <tableColumn id="2" xr3:uid="{89C1D28F-142B-4561-8500-1D04F92B297C}" name="Tipo Documento" dataDxfId="397"/>
-    <tableColumn id="3" xr3:uid="{D90392C4-A04B-4E1E-9602-23CB09E80210}" name="Contraseña" dataDxfId="396" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="16" xr3:uid="{D4643556-93D1-4D92-80E4-8FA95CEAAB10}" name="Primer Nombre" dataDxfId="395" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="17" xr3:uid="{6C9A7681-B3A2-4741-82B5-C182F906DCAD}" name="Segundo Nombre" dataDxfId="394"/>
-    <tableColumn id="4" xr3:uid="{A88E4EAA-2C54-43A6-9D24-298243725419}" name="Primer Apellido" dataDxfId="393"/>
-    <tableColumn id="18" xr3:uid="{7F995AF7-B770-4CD1-A98B-9E63F703A906}" name="Segundo Apellido" dataDxfId="392"/>
-    <tableColumn id="5" xr3:uid="{2B0026E5-0853-4060-B860-39793C0BBA4F}" name="Correo1" dataDxfId="391" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="6" xr3:uid="{5CDB0439-6DCE-4D03-8D89-14CA05CF598C}" name="Correo2" dataDxfId="390" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="7" xr3:uid="{DA24CD4D-EF4A-4AFE-ABF5-FDE103298085}" name="Contacto1" dataDxfId="389"/>
-    <tableColumn id="19" xr3:uid="{62E8138E-A6B4-48F5-BC4E-A01D4CF3891A}" name="Contacto2" dataDxfId="388"/>
-    <tableColumn id="10" xr3:uid="{094D2A78-7FDE-4EEC-8B40-39AEA1121445}" name="Fecha Nacimiento" dataDxfId="387"/>
-    <tableColumn id="11" xr3:uid="{BFFAA792-B23A-472D-87FC-C4C48881E11C}" name="Foto" dataDxfId="386"/>
-    <tableColumn id="12" xr3:uid="{F3DC8E24-C168-4949-985D-A6A067485832}" name="ID Rol" dataDxfId="385"/>
-    <tableColumn id="13" xr3:uid="{902DCEDE-9416-42C2-B8F6-D6696E4F4DE0}" name="ID Curso" dataDxfId="384"/>
-    <tableColumn id="14" xr3:uid="{26883128-1C06-49E2-8370-1D79D0CA18C6}" name="ID Grado" dataDxfId="383"/>
-    <tableColumn id="15" xr3:uid="{A88E5EEE-5442-4085-B8FD-79C27349FEF2}" name="ID Jornada" dataDxfId="382"/>
+    <tableColumn id="1" xr3:uid="{7318D55B-472C-40E5-B77D-F547B319090B}" name="N.O Documento" dataDxfId="394"/>
+    <tableColumn id="2" xr3:uid="{89C1D28F-142B-4561-8500-1D04F92B297C}" name="Tipo Documento" dataDxfId="393"/>
+    <tableColumn id="3" xr3:uid="{D90392C4-A04B-4E1E-9602-23CB09E80210}" name="Contraseña" dataDxfId="392" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="16" xr3:uid="{D4643556-93D1-4D92-80E4-8FA95CEAAB10}" name="Primer Nombre" dataDxfId="391" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="17" xr3:uid="{6C9A7681-B3A2-4741-82B5-C182F906DCAD}" name="Segundo Nombre" dataDxfId="390"/>
+    <tableColumn id="4" xr3:uid="{A88E4EAA-2C54-43A6-9D24-298243725419}" name="Primer Apellido" dataDxfId="389"/>
+    <tableColumn id="18" xr3:uid="{7F995AF7-B770-4CD1-A98B-9E63F703A906}" name="Segundo Apellido" dataDxfId="388"/>
+    <tableColumn id="5" xr3:uid="{2B0026E5-0853-4060-B860-39793C0BBA4F}" name="Correo1" dataDxfId="387" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="6" xr3:uid="{5CDB0439-6DCE-4D03-8D89-14CA05CF598C}" name="Correo2" dataDxfId="386" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="7" xr3:uid="{DA24CD4D-EF4A-4AFE-ABF5-FDE103298085}" name="Contacto1" dataDxfId="385"/>
+    <tableColumn id="19" xr3:uid="{62E8138E-A6B4-48F5-BC4E-A01D4CF3891A}" name="Contacto2" dataDxfId="384"/>
+    <tableColumn id="10" xr3:uid="{094D2A78-7FDE-4EEC-8B40-39AEA1121445}" name="Fecha Nacimiento" dataDxfId="383"/>
+    <tableColumn id="11" xr3:uid="{BFFAA792-B23A-472D-87FC-C4C48881E11C}" name="Foto" dataDxfId="382"/>
+    <tableColumn id="12" xr3:uid="{F3DC8E24-C168-4949-985D-A6A067485832}" name="ID Rol" dataDxfId="381"/>
+    <tableColumn id="13" xr3:uid="{902DCEDE-9416-42C2-B8F6-D6696E4F4DE0}" name="ID Curso" dataDxfId="380"/>
+    <tableColumn id="14" xr3:uid="{26883128-1C06-49E2-8370-1D79D0CA18C6}" name="ID Grado" dataDxfId="379"/>
+    <tableColumn id="15" xr3:uid="{A88E5EEE-5442-4085-B8FD-79C27349FEF2}" name="ID Jornada" dataDxfId="378"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{B4E6B38E-6C88-42B1-8DEB-93CBE5CEAE3C}" name="Tabla712" displayName="Tabla712" ref="B17:H20" totalsRowShown="0" headerRowDxfId="381" dataDxfId="380">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{B4E6B38E-6C88-42B1-8DEB-93CBE5CEAE3C}" name="Tabla712" displayName="Tabla712" ref="B17:H20" totalsRowShown="0" headerRowDxfId="377" dataDxfId="376">
   <autoFilter ref="B17:H20" xr:uid="{B4E6B38E-6C88-42B1-8DEB-93CBE5CEAE3C}"/>
   <tableColumns count="7">
-    <tableColumn id="26" xr3:uid="{8AF70358-63E4-43A6-A3D9-C7C3EE751CD4}" name="ID Aula" dataDxfId="379"/>
-    <tableColumn id="1" xr3:uid="{89B42342-4ADD-4D7E-AC89-620D0C1ABDC8}" name="Nombre Aula" dataDxfId="378"/>
-    <tableColumn id="2" xr3:uid="{73FE6164-DAC1-445D-9285-21753BE06E09}" name="Nombre Materia" dataDxfId="377"/>
-    <tableColumn id="3" xr3:uid="{AA5EB5CF-88BF-4D45-BE7F-6273D62E643B}" name="Profesor" dataDxfId="376"/>
-    <tableColumn id="4" xr3:uid="{FCCA3711-19FE-47E1-A4F6-E9EB0609ED9C}" name="Curso" dataDxfId="375"/>
-    <tableColumn id="13" xr3:uid="{36CBA36C-F8E3-428F-B8F4-7CD3613959B9}" name="ID Anuncios" dataDxfId="374"/>
-    <tableColumn id="11" xr3:uid="{DB1BAE2E-C404-461A-9205-A2AE0B6C0904}" name="ID Trabajos" dataDxfId="373"/>
+    <tableColumn id="26" xr3:uid="{8AF70358-63E4-43A6-A3D9-C7C3EE751CD4}" name="ID Aula" dataDxfId="375"/>
+    <tableColumn id="1" xr3:uid="{89B42342-4ADD-4D7E-AC89-620D0C1ABDC8}" name="Nombre Aula" dataDxfId="374"/>
+    <tableColumn id="2" xr3:uid="{73FE6164-DAC1-445D-9285-21753BE06E09}" name="Nombre Materia" dataDxfId="373"/>
+    <tableColumn id="3" xr3:uid="{AA5EB5CF-88BF-4D45-BE7F-6273D62E643B}" name="Profesor" dataDxfId="372"/>
+    <tableColumn id="4" xr3:uid="{FCCA3711-19FE-47E1-A4F6-E9EB0609ED9C}" name="Curso" dataDxfId="371"/>
+    <tableColumn id="13" xr3:uid="{36CBA36C-F8E3-428F-B8F4-7CD3613959B9}" name="ID Anuncios" dataDxfId="370"/>
+    <tableColumn id="11" xr3:uid="{DB1BAE2E-C404-461A-9205-A2AE0B6C0904}" name="ID Trabajos" dataDxfId="369"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3A1FB0EA-C16F-49A3-9AA6-F6DC96A00624}" name="Tabla813" displayName="Tabla813" ref="B31:G34" totalsRowShown="0" headerRowDxfId="372" dataDxfId="371">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3A1FB0EA-C16F-49A3-9AA6-F6DC96A00624}" name="Tabla813" displayName="Tabla813" ref="B31:G34" totalsRowShown="0" headerRowDxfId="368" dataDxfId="367">
   <autoFilter ref="B31:G34" xr:uid="{3A1FB0EA-C16F-49A3-9AA6-F6DC96A00624}"/>
   <tableColumns count="6">
-    <tableColumn id="6" xr3:uid="{ADC13DE6-F7E6-4F93-B332-4C1E06105739}" name="ID Horario" dataDxfId="370"/>
-    <tableColumn id="1" xr3:uid="{D0921E14-AA59-471F-924C-188298E3FA55}" name="Titulo Horario" dataDxfId="369"/>
-    <tableColumn id="2" xr3:uid="{9C10F91B-3DBF-4ECF-AE8A-DFBBC5FE4A55}" name="Imagen Horario" dataDxfId="368"/>
-    <tableColumn id="3" xr3:uid="{F559656E-EAB9-46AE-A609-9ED01C42C573}" name="Descripcion" dataDxfId="367"/>
-    <tableColumn id="4" xr3:uid="{D0CA5FE1-0E65-4616-A1DA-431EEFC38457}" name="Curso" dataDxfId="366"/>
-    <tableColumn id="5" xr3:uid="{3CAB56CE-4D4C-4BC8-9664-27828254EC8D}" name="ID Profesor" dataDxfId="365"/>
+    <tableColumn id="6" xr3:uid="{ADC13DE6-F7E6-4F93-B332-4C1E06105739}" name="ID Horario" dataDxfId="366"/>
+    <tableColumn id="1" xr3:uid="{D0921E14-AA59-471F-924C-188298E3FA55}" name="Titulo Horario" dataDxfId="365"/>
+    <tableColumn id="2" xr3:uid="{9C10F91B-3DBF-4ECF-AE8A-DFBBC5FE4A55}" name="Imagen Horario" dataDxfId="364"/>
+    <tableColumn id="3" xr3:uid="{F559656E-EAB9-46AE-A609-9ED01C42C573}" name="Descripcion" dataDxfId="363"/>
+    <tableColumn id="4" xr3:uid="{D0CA5FE1-0E65-4616-A1DA-431EEFC38457}" name="Curso" dataDxfId="362"/>
+    <tableColumn id="5" xr3:uid="{3CAB56CE-4D4C-4BC8-9664-27828254EC8D}" name="ID Profesor" dataDxfId="361"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{B0F01AAB-20DA-4CAD-879F-544D80A978C1}" name="Tabla1927668614" displayName="Tabla1927668614" ref="B38:L41" totalsRowShown="0" headerRowDxfId="364" dataDxfId="362" headerRowBorderDxfId="363" tableBorderDxfId="361" totalsRowBorderDxfId="360">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{B0F01AAB-20DA-4CAD-879F-544D80A978C1}" name="Tabla1927668614" displayName="Tabla1927668614" ref="B38:L41" totalsRowShown="0" headerRowDxfId="360" dataDxfId="358" headerRowBorderDxfId="359" tableBorderDxfId="357" totalsRowBorderDxfId="356">
   <autoFilter ref="B38:L41" xr:uid="{B0F01AAB-20DA-4CAD-879F-544D80A978C1}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{2DBE5779-A106-4A63-99B8-3A4006710F03}" name="ID Noticias" dataDxfId="359"/>
-    <tableColumn id="2" xr3:uid="{95710523-C973-4A3D-A32D-454004AE9EF4}" name="Titulo" dataDxfId="358"/>
-    <tableColumn id="3" xr3:uid="{39ACE949-5961-4035-B992-5C7469ED880B}" name="Encabezado" dataDxfId="357"/>
-    <tableColumn id="4" xr3:uid="{8165BAAE-081D-4E6F-AC58-CB7128D8A68A}" name="DescripcionPrincipal" dataDxfId="356"/>
-    <tableColumn id="5" xr3:uid="{BF76C591-5E12-4B63-ABB0-7044E8738CCF}" name="Descripcion2 (opcional)" dataDxfId="355"/>
-    <tableColumn id="6" xr3:uid="{EB04576D-5BCE-43E2-9831-76B0AB3542F6}" name="Descripcion3 (opcional)" dataDxfId="354"/>
-    <tableColumn id="7" xr3:uid="{5898BF31-F525-4B36-BEC2-940C7028EB11}" name="ImagenEncabezado" dataDxfId="353"/>
-    <tableColumn id="8" xr3:uid="{C23A3BAA-FD8A-4FE4-AC02-CF167591CDE2}" name="ImagenPrincipal" dataDxfId="352"/>
-    <tableColumn id="9" xr3:uid="{68F1C1A9-51E9-4EB2-8367-F8F498F6838C}" name="ImagenSecundaria" dataDxfId="351"/>
-    <tableColumn id="10" xr3:uid="{79F4C26D-8709-470B-B84B-FDABE1358484}" name="Fecha" dataDxfId="350"/>
-    <tableColumn id="11" xr3:uid="{C1A433FD-95C2-401E-A531-CD743CA4823C}" name="Tipo" dataDxfId="349"/>
+    <tableColumn id="1" xr3:uid="{2DBE5779-A106-4A63-99B8-3A4006710F03}" name="ID Noticias" dataDxfId="355"/>
+    <tableColumn id="2" xr3:uid="{95710523-C973-4A3D-A32D-454004AE9EF4}" name="Titulo" dataDxfId="354"/>
+    <tableColumn id="3" xr3:uid="{39ACE949-5961-4035-B992-5C7469ED880B}" name="Encabezado" dataDxfId="353"/>
+    <tableColumn id="4" xr3:uid="{8165BAAE-081D-4E6F-AC58-CB7128D8A68A}" name="DescripcionPrincipal" dataDxfId="352"/>
+    <tableColumn id="5" xr3:uid="{BF76C591-5E12-4B63-ABB0-7044E8738CCF}" name="Descripcion2 (opcional)" dataDxfId="351"/>
+    <tableColumn id="6" xr3:uid="{EB04576D-5BCE-43E2-9831-76B0AB3542F6}" name="Descripcion3 (opcional)" dataDxfId="350"/>
+    <tableColumn id="7" xr3:uid="{5898BF31-F525-4B36-BEC2-940C7028EB11}" name="ImagenEncabezado" dataDxfId="349"/>
+    <tableColumn id="8" xr3:uid="{C23A3BAA-FD8A-4FE4-AC02-CF167591CDE2}" name="ImagenPrincipal" dataDxfId="348"/>
+    <tableColumn id="9" xr3:uid="{68F1C1A9-51E9-4EB2-8367-F8F498F6838C}" name="ImagenSecundaria" dataDxfId="347"/>
+    <tableColumn id="10" xr3:uid="{79F4C26D-8709-470B-B84B-FDABE1358484}" name="Fecha" dataDxfId="346"/>
+    <tableColumn id="11" xr3:uid="{C1A433FD-95C2-401E-A531-CD743CA4823C}" name="Tipo" dataDxfId="345"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="66" xr:uid="{432C6F4F-50D0-406E-8976-6AB17A04F319}" name="Tabla29416967" displayName="Tabla29416967" ref="B10:C13" totalsRowShown="0" headerRowDxfId="348" dataDxfId="346" headerRowBorderDxfId="347" tableBorderDxfId="345" totalsRowBorderDxfId="344">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="66" xr:uid="{432C6F4F-50D0-406E-8976-6AB17A04F319}" name="Tabla29416967" displayName="Tabla29416967" ref="B10:C13" totalsRowShown="0" headerRowDxfId="344" dataDxfId="342" headerRowBorderDxfId="343" tableBorderDxfId="341" totalsRowBorderDxfId="340">
   <autoFilter ref="B10:C13" xr:uid="{432C6F4F-50D0-406E-8976-6AB17A04F319}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C90D5CA0-9DF8-49D3-9862-BFFAE8447A18}" name="ID Curso" dataDxfId="343"/>
-    <tableColumn id="2" xr3:uid="{39FA17FE-5CED-4E8C-9BDC-F76978CFA24A}" name="Nombre Curso" dataDxfId="342"/>
+    <tableColumn id="1" xr3:uid="{C90D5CA0-9DF8-49D3-9862-BFFAE8447A18}" name="ID Curso" dataDxfId="339"/>
+    <tableColumn id="2" xr3:uid="{39FA17FE-5CED-4E8C-9BDC-F76978CFA24A}" name="Nombre Curso" dataDxfId="338"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16986,14 +16855,14 @@
       <c r="B31" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="I31" s="36" t="s">
+      <c r="H31" s="36" t="s">
         <v>175</v>
       </c>
+      <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="43" t="s">
@@ -17006,30 +16875,27 @@
         <v>207</v>
       </c>
       <c r="E32" s="43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F32" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="I32" s="55" t="s">
+      <c r="H32" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="J32" s="41" t="s">
+      <c r="I32" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="K32" s="42" t="s">
+      <c r="J32" s="42" t="s">
         <v>43</v>
       </c>
+      <c r="K32" s="43" t="s">
+        <v>5</v>
+      </c>
       <c r="L32" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="N32" s="36" t="s">
+      <c r="M32" s="36" t="s">
         <v>139</v>
       </c>
     </row>
@@ -17043,31 +16909,28 @@
       <c r="D33" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="F33" s="44">
+      <c r="E33" s="44">
         <v>45698</v>
       </c>
-      <c r="G33" s="25" t="s">
+      <c r="F33" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I33" s="53" t="s">
+      <c r="H33" s="53" t="s">
         <v>171</v>
       </c>
-      <c r="J33" s="26" t="s">
+      <c r="I33" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="K33" s="44">
+      <c r="J33" s="44">
         <v>45698</v>
       </c>
+      <c r="K33" s="25" t="s">
+        <v>96</v>
+      </c>
       <c r="L33" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="M33" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="N33" s="54" t="s">
+      <c r="M33" s="54" t="s">
         <v>146</v>
       </c>
     </row>
@@ -17081,31 +16944,28 @@
       <c r="D34" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="F34" s="44">
+      <c r="E34" s="44">
         <v>45700</v>
       </c>
-      <c r="G34" s="25" t="s">
+      <c r="F34" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="I34" s="53" t="s">
+      <c r="H34" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="J34" s="26" t="s">
+      <c r="I34" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="K34" s="44">
+      <c r="J34" s="44">
         <v>45700</v>
       </c>
+      <c r="K34" s="25" t="s">
+        <v>97</v>
+      </c>
       <c r="L34" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="M34" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="N34" s="54" t="s">
+      <c r="M34" s="54" t="s">
         <v>147</v>
       </c>
     </row>
@@ -17119,33 +16979,33 @@
       <c r="D35" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E35" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="F35" s="44">
+      <c r="E35" s="44">
         <v>45703</v>
       </c>
-      <c r="G35" s="25" t="s">
+      <c r="F35" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="I35" s="53" t="s">
+      <c r="H35" s="53" t="s">
         <v>173</v>
       </c>
-      <c r="J35" s="26" t="s">
+      <c r="I35" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="K35" s="44">
+      <c r="J35" s="44">
         <v>45703</v>
       </c>
+      <c r="K35" s="25" t="s">
+        <v>98</v>
+      </c>
       <c r="L35" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="M35" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="N35" s="54" t="s">
+      <c r="M35" s="54" t="s">
         <v>148</v>
       </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="H37" s="1"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B38" s="51" t="s">
@@ -17154,86 +17014,155 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
+      <c r="H38" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="L38" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B39" s="57" t="s">
         <v>179</v>
       </c>
       <c r="C39" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="E39" s="41" t="s">
+      <c r="D39" s="41" t="s">
         <v>32</v>
       </c>
+      <c r="E39" s="58" t="s">
+        <v>5</v>
+      </c>
       <c r="F39" s="58" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="58" t="s">
         <v>139</v>
+      </c>
+      <c r="H39" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="I39" s="58" t="s">
+        <v>223</v>
+      </c>
+      <c r="J39" s="58" t="s">
+        <v>224</v>
+      </c>
+      <c r="L39" s="57" t="s">
+        <v>230</v>
+      </c>
+      <c r="M39" s="58" t="s">
+        <v>223</v>
+      </c>
+      <c r="N39" s="58" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B40" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="56">
+        <v>45698</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="I40" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="56">
-        <v>45698</v>
-      </c>
-      <c r="E40" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="G40" s="27" t="s">
-        <v>146</v>
+      <c r="J40" s="56" t="s">
+        <v>225</v>
+      </c>
+      <c r="L40" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="M40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N40" s="56" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B41" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="56">
+        <v>45700</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F41" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="I41" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="D41" s="56">
-        <v>45700</v>
-      </c>
-      <c r="E41" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="F41" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="G41" s="27" t="s">
-        <v>147</v>
+      <c r="J41" s="56" t="s">
+        <v>226</v>
+      </c>
+      <c r="L41" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="M41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N41" s="56" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B42" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="C42" s="27" t="s">
+      <c r="C42" s="56">
+        <v>45703</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F42" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="H42" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="I42" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="56">
-        <v>45703</v>
-      </c>
-      <c r="E42" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="F42" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="G42" s="27" t="s">
-        <v>148</v>
+      <c r="J42" s="56" t="s">
+        <v>227</v>
+      </c>
+      <c r="L42" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="M42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N42" s="56" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.2">
@@ -17462,7 +17391,7 @@
     <col min="6" max="6" width="23.140625" customWidth="1"/>
     <col min="7" max="7" width="21.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.28515625" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="9" max="9" width="24.28515625" customWidth="1"/>
     <col min="10" max="10" width="21.7109375" customWidth="1"/>
     <col min="11" max="11" width="19.7109375" customWidth="1"/>
     <col min="12" max="12" width="18.5703125" customWidth="1"/>
@@ -18177,14 +18106,14 @@
       <c r="B31" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="I31" s="36" t="s">
+      <c r="H31" s="36" t="s">
         <v>175</v>
       </c>
+      <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="43" t="s">
@@ -18197,30 +18126,27 @@
         <v>207</v>
       </c>
       <c r="E32" s="43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F32" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="I32" s="55" t="s">
+      <c r="H32" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="J32" s="41" t="s">
+      <c r="I32" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="K32" s="42" t="s">
+      <c r="J32" s="42" t="s">
         <v>43</v>
       </c>
+      <c r="K32" s="43" t="s">
+        <v>5</v>
+      </c>
       <c r="L32" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="N32" s="36" t="s">
+      <c r="M32" s="36" t="s">
         <v>139</v>
       </c>
     </row>
@@ -18234,31 +18160,28 @@
       <c r="D33" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="F33" s="44">
+      <c r="E33" s="44">
         <v>45698</v>
       </c>
-      <c r="G33" s="25" t="s">
+      <c r="F33" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I33" s="53" t="s">
+      <c r="H33" s="53" t="s">
         <v>171</v>
       </c>
-      <c r="J33" s="26" t="s">
+      <c r="I33" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="K33" s="44">
+      <c r="J33" s="44">
         <v>45698</v>
       </c>
+      <c r="K33" s="25" t="s">
+        <v>96</v>
+      </c>
       <c r="L33" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="M33" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="N33" s="54" t="s">
+      <c r="M33" s="54" t="s">
         <v>146</v>
       </c>
     </row>
@@ -18272,31 +18195,28 @@
       <c r="D34" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="F34" s="44">
+      <c r="E34" s="44">
         <v>45700</v>
       </c>
-      <c r="G34" s="25" t="s">
+      <c r="F34" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="I34" s="53" t="s">
+      <c r="H34" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="J34" s="26" t="s">
+      <c r="I34" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="K34" s="44">
+      <c r="J34" s="44">
         <v>45700</v>
       </c>
+      <c r="K34" s="25" t="s">
+        <v>97</v>
+      </c>
       <c r="L34" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="M34" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="N34" s="54" t="s">
+      <c r="M34" s="54" t="s">
         <v>147</v>
       </c>
     </row>
@@ -18310,33 +18230,31 @@
       <c r="D35" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E35" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="F35" s="44">
+      <c r="E35" s="44">
         <v>45703</v>
       </c>
-      <c r="G35" s="25" t="s">
+      <c r="F35" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="I35" s="53" t="s">
+      <c r="H35" s="53" t="s">
         <v>173</v>
       </c>
-      <c r="J35" s="26" t="s">
+      <c r="I35" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="K35" s="44">
+      <c r="J35" s="44">
         <v>45703</v>
       </c>
+      <c r="K35" s="25" t="s">
+        <v>98</v>
+      </c>
       <c r="L35" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="M35" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="N35" s="54" t="s">
+      <c r="M35" s="54" t="s">
         <v>148</v>
       </c>
+      <c r="N35" s="1"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B38" s="51" t="s">
@@ -18345,86 +18263,155 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
+      <c r="H38" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="L38" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B39" s="57" t="s">
         <v>179</v>
       </c>
       <c r="C39" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="E39" s="41" t="s">
+      <c r="D39" s="41" t="s">
         <v>32</v>
       </c>
+      <c r="E39" s="58" t="s">
+        <v>5</v>
+      </c>
       <c r="F39" s="58" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="58" t="s">
         <v>139</v>
+      </c>
+      <c r="H39" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="I39" s="58" t="s">
+        <v>223</v>
+      </c>
+      <c r="J39" s="58" t="s">
+        <v>224</v>
+      </c>
+      <c r="L39" s="57" t="s">
+        <v>230</v>
+      </c>
+      <c r="M39" s="58" t="s">
+        <v>223</v>
+      </c>
+      <c r="N39" s="58" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B40" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="56">
+        <v>45698</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="I40" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="56">
-        <v>45698</v>
-      </c>
-      <c r="E40" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="G40" s="27" t="s">
-        <v>146</v>
+      <c r="J40" s="56" t="s">
+        <v>225</v>
+      </c>
+      <c r="L40" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="M40" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N40" s="56" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B41" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="56">
+        <v>45700</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F41" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="I41" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="D41" s="56">
-        <v>45700</v>
-      </c>
-      <c r="E41" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="F41" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="G41" s="27" t="s">
-        <v>147</v>
+      <c r="J41" s="56" t="s">
+        <v>226</v>
+      </c>
+      <c r="L41" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="M41" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N41" s="56" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B42" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="C42" s="27" t="s">
+      <c r="C42" s="56">
+        <v>45703</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F42" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="H42" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="I42" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="56">
-        <v>45703</v>
-      </c>
-      <c r="E42" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="F42" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="G42" s="27" t="s">
-        <v>148</v>
+      <c r="J42" s="56" t="s">
+        <v>227</v>
+      </c>
+      <c r="L42" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="M42" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="N42" s="56" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.2">
@@ -18610,6 +18597,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I5" r:id="rId1" xr:uid="{52C576A4-4468-40DC-91F9-0B2231A90104}"/>
     <hyperlink ref="J5" r:id="rId2" xr:uid="{49EFD259-6A91-4B9B-9147-BBA0B8EFD939}"/>
@@ -18619,8 +18607,8 @@
     <hyperlink ref="J7" r:id="rId6" xr:uid="{EDC4DE84-727A-4AB5-A984-E9FFDD701AA0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
   <tableParts count="16">
-    <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
     <tablePart r:id="rId10"/>
@@ -18636,6 +18624,7 @@
     <tablePart r:id="rId20"/>
     <tablePart r:id="rId21"/>
     <tablePart r:id="rId22"/>
+    <tablePart r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>